--- a/03_内部設計/022-クラス仕様書/util/PagingUtilのクラス仕様書.xlsx
+++ b/03_内部設計/022-クラス仕様書/util/PagingUtilのクラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561B6B97-7D0B-4993-B1DB-EFAA447CBBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7D727A-D797-4C12-AFBA-4B810D0D6B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5868" yWindow="-96" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（paging）'!$A$1:$BI$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（paging）'!$A$1:$BI$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="86">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -213,10 +213,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.3) int型の変数、nowPageを１で初期化する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>3.1) JSPで押下されたボタンから、データをgetParameterメソッドで取得する。</t>
     <rPh sb="11" eb="12">
       <t>ガタ</t>
@@ -246,64 +242,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>List&lt;ItemsDTO&gt;型のArrayList、splitedListを生成する。</t>
-    <rPh sb="14" eb="15">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4) pageの値からif-else if文で条件分岐処理を行う。</t>
-    <rPh sb="10" eb="11">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="25" eb="31">
-      <t>ジョウケンブンキショリ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.1) pageがnullの場合(初回アクセス時)</t>
-    <rPh sb="17" eb="19">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ショカイ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>3.4.1.1) 最大10件分のデータをf、or文でsplitedListに格納する</t>
     <rPh sb="24" eb="25">
       <t>ブン</t>
     </rPh>
     <rPh sb="38" eb="40">
       <t>カクノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.2) pageの値が"次へ"の場合</t>
-    <rPh sb="12" eb="13">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -321,39 +265,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.1.1) 取得したデータはString型の変数、pageに代入する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.2.2) (取得したページ数) + 1をnowPageに代入する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.2.3) int型の変数、fromIndexを宣言し、</t>
-    <rPh sb="12" eb="13">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>センゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>splitedListに最初に格納する検索結果の要素番号を代入する。</t>
-  </si>
-  <si>
-    <t>3.4.2.4) for文とfromIndexを用いて、最大10件分のデータをsplitedListに格納する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.3) pageの値が"前へ"の場合</t>
-    <rPh sb="15" eb="16">
-      <t>マエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.4.3.1) 現在表示しているページ数をJSPから取得する。</t>
@@ -366,68 +278,6 @@
     <rPh sb="27" eb="29">
       <t>シュトク</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.3.3) int型の変数、fromIndexを宣言し、</t>
-    <rPh sb="12" eb="13">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>センゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.3.4) for文とfromIndexを用いて、最大10件分のデータをsplitedListに格納する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.3.2) (取得したページ数) - 1をnowPageに代入する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.4) pageの値が数値の場合</t>
-    <rPh sb="12" eb="13">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.4.1) 現在表示しているページ数をJSPから取得し、nowPageに代入する。</t>
-    <rPh sb="9" eb="13">
-      <t>ゲンザイヒョウジ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ダイニュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.4.2) int型の変数、fromIndexを宣言し、</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.4.3) for文とfromIndexを用いて、最大10件分のデータをsplitedListに格納する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4.1) "nowPage"でnowPage</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -497,52 +347,7 @@
     <t>resultList</t>
   </si>
   <si>
-    <t>int型の変数、endPageを0で初期化する。</t>
-    <rPh sb="3" eb="4">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヘンスウ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ショキカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.1) resultListの要素数を10で割った余りが0の場合、endPageに以下の式を代入する。</t>
-    <rPh sb="16" eb="19">
-      <t>ヨウソスウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>アマ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>シキ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ダイニュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>(resultListの要素数) / 10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.2) 2.1以外の場合、endPageに以下の式を代入する。</t>
-    <rPh sb="8" eb="10">
-      <t>イガイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -593,6 +398,203 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>1.1) HttpServletRequestクラスのgetSessionメソッドを呼び出す。</t>
+    <rPh sb="42" eb="43">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>request</t>
+  </si>
+  <si>
+    <t>int型の変数、endを0で初期化する。</t>
+    <rPh sb="3" eb="4">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ショキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.1) resultListの要素数を10で割った余りが0の場合、endに以下の式を代入する。</t>
+    <rPh sb="16" eb="19">
+      <t>ヨウソスウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ダイニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.2) 2.1以外の場合、endに以下の式を代入する。</t>
+    <rPh sb="8" eb="10">
+      <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.3) HttpSessionクラスのsetAttributeメソッドを呼び出し、引数に"end"とendを渡す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.1.1) 取得したデータはString型の変数、requestedに代入する。</t>
+  </si>
+  <si>
+    <t>3.4) requestedの値からif-else if文で条件分岐処理を行う。</t>
+    <rPh sb="15" eb="16">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="30" eb="36">
+      <t>ジョウケンブンキショリ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.4.1) requestedがnullの場合(初回アクセス時)</t>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.4.2) requestedの値が"次へ"の場合</t>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.4.3) requestedの値が"前へ"の場合</t>
+    <rPh sb="20" eb="21">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.4.4) requestedの値が数値の場合</t>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.3) int型の変数、nowを１で初期化する。</t>
+  </si>
+  <si>
+    <t>3.4.2.2) (取得したページ数) + 1をnowに代入する。</t>
+  </si>
+  <si>
+    <t>3.4.3.2) (取得したページ数) - 1をnowに代入する。</t>
+  </si>
+  <si>
+    <t>3.4.4.1) 現在表示しているページ数をJSPから取得し、nowに代入する。</t>
+    <rPh sb="9" eb="13">
+      <t>ゲンザイヒョウジ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ダイニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.1) "now"でnow</t>
+  </si>
+  <si>
+    <t>3.4.2.3) int型の変数、startを宣言し、</t>
+    <rPh sb="12" eb="13">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.4.2.4) for文とstartを用いて、最大10件分のデータをsplitedListに格納する。</t>
+  </si>
+  <si>
+    <t>3.4.3.3) int型の変数、startを宣言し、</t>
+    <rPh sb="12" eb="13">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.4.3.4) for文とstartを用いて、最大10件分のデータをsplitedListに格納する。</t>
+  </si>
+  <si>
+    <t>3.4.4.2) int型の変数、startを宣言し、</t>
+  </si>
+  <si>
+    <t>3.4.4.3) for文とstartを用いて、最大10件分のデータをsplitedListに格納する。</t>
+  </si>
+  <si>
+    <t>3.2.1) List&lt;ItemsDTO&gt;型のArrayList、splitedListを生成する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -602,7 +604,7 @@
     <numFmt numFmtId="176" formatCode="[$-411]yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -640,6 +642,12 @@
     <font>
       <b/>
       <sz val="10.5"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -928,11 +936,26 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -943,13 +966,13 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -958,35 +981,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -997,8 +999,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1350,85 +1358,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="32" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="33" t="s">
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="32" t="s">
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="33" t="s">
-        <v>67</v>
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44"/>
+      <c r="AE1" s="43" t="s">
+        <v>49</v>
       </c>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="33"/>
-      <c r="AN1" s="33"/>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="32" t="s">
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="43"/>
+      <c r="AK1" s="43"/>
+      <c r="AL1" s="43"/>
+      <c r="AM1" s="43"/>
+      <c r="AN1" s="43"/>
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="43"/>
+      <c r="AQ1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="33" t="s">
+      <c r="AR1" s="44"/>
+      <c r="AS1" s="44"/>
+      <c r="AT1" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="33"/>
-      <c r="AV1" s="33"/>
-      <c r="AW1" s="33"/>
-      <c r="AX1" s="33"/>
-      <c r="AY1" s="33"/>
-      <c r="AZ1" s="33"/>
-      <c r="BA1" s="32" t="s">
+      <c r="AU1" s="43"/>
+      <c r="AV1" s="43"/>
+      <c r="AW1" s="43"/>
+      <c r="AX1" s="43"/>
+      <c r="AY1" s="43"/>
+      <c r="AZ1" s="43"/>
+      <c r="BA1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-      <c r="BD1" s="40">
+      <c r="BB1" s="44"/>
+      <c r="BC1" s="44"/>
+      <c r="BD1" s="45">
         <v>45555</v>
       </c>
-      <c r="BE1" s="40"/>
-      <c r="BF1" s="40"/>
-      <c r="BG1" s="40"/>
-      <c r="BH1" s="40"/>
-      <c r="BI1" s="40"/>
+      <c r="BE1" s="45"/>
+      <c r="BF1" s="45"/>
+      <c r="BG1" s="45"/>
+      <c r="BH1" s="45"/>
+      <c r="BI1" s="45"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1628,82 +1636,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="32" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="32" t="s">
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="33" t="str">
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="43" t="str">
         <f>G5</f>
         <v>PagingUtil</v>
       </c>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="33"/>
-      <c r="AN2" s="33"/>
-      <c r="AO2" s="33"/>
-      <c r="AP2" s="33"/>
-      <c r="AQ2" s="32" t="s">
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="33" t="s">
-        <v>68</v>
+      <c r="AR2" s="44"/>
+      <c r="AS2" s="44"/>
+      <c r="AT2" s="43" t="s">
+        <v>50</v>
       </c>
-      <c r="AU2" s="33"/>
-      <c r="AV2" s="33"/>
-      <c r="AW2" s="33"/>
-      <c r="AX2" s="33"/>
-      <c r="AY2" s="33"/>
-      <c r="AZ2" s="33"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="43"/>
+      <c r="AX2" s="43"/>
+      <c r="AY2" s="43"/>
+      <c r="AZ2" s="43"/>
+      <c r="BA2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="34">
+      <c r="BB2" s="44"/>
+      <c r="BC2" s="44"/>
+      <c r="BD2" s="39">
         <v>45566</v>
       </c>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="36"/>
+      <c r="BE2" s="40"/>
+      <c r="BF2" s="40"/>
+      <c r="BG2" s="40"/>
+      <c r="BH2" s="40"/>
+      <c r="BI2" s="41"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1966,16 +1974,16 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="38" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
@@ -2033,14 +2041,14 @@
       <c r="BI4" s="38"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
       <c r="G5" s="38" t="s">
         <v>31</v>
       </c>
@@ -2100,14 +2108,14 @@
       <c r="BI5" s="38"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
       <c r="G6" s="38" t="s">
         <v>12</v>
       </c>
@@ -2133,14 +2141,14 @@
       <c r="AA6" s="38"/>
       <c r="AB6" s="38"/>
       <c r="AC6" s="38"/>
-      <c r="AD6" s="37" t="s">
+      <c r="AD6" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="37"/>
-      <c r="AG6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="37"/>
+      <c r="AE6" s="36"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="36"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
       <c r="AJ6" s="38" t="s">
         <v>28</v>
       </c>
@@ -2171,737 +2179,722 @@
       <c r="BI6" s="38"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37" t="s">
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37" t="s">
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="36"/>
+      <c r="AB8" s="36"/>
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="36"/>
+      <c r="AE8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="37"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="37" t="s">
+      <c r="AF8" s="36"/>
+      <c r="AG8" s="36"/>
+      <c r="AH8" s="36"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="36"/>
+      <c r="AK8" s="36"/>
+      <c r="AL8" s="36"/>
+      <c r="AM8" s="36"/>
+      <c r="AN8" s="36"/>
+      <c r="AO8" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="37"/>
-      <c r="AS8" s="37"/>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="37"/>
-      <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="37"/>
-      <c r="AY8" s="37"/>
-      <c r="AZ8" s="37"/>
-      <c r="BA8" s="37"/>
-      <c r="BB8" s="37"/>
-      <c r="BC8" s="37"/>
-      <c r="BD8" s="37"/>
-      <c r="BE8" s="37"/>
-      <c r="BF8" s="37"/>
-      <c r="BG8" s="37"/>
-      <c r="BH8" s="37"/>
-      <c r="BI8" s="37"/>
+      <c r="AP8" s="36"/>
+      <c r="AQ8" s="36"/>
+      <c r="AR8" s="36"/>
+      <c r="AS8" s="36"/>
+      <c r="AT8" s="36"/>
+      <c r="AU8" s="36"/>
+      <c r="AV8" s="36"/>
+      <c r="AW8" s="36"/>
+      <c r="AX8" s="36"/>
+      <c r="AY8" s="36"/>
+      <c r="AZ8" s="36"/>
+      <c r="BA8" s="36"/>
+      <c r="BB8" s="36"/>
+      <c r="BC8" s="36"/>
+      <c r="BD8" s="36"/>
+      <c r="BE8" s="36"/>
+      <c r="BF8" s="36"/>
+      <c r="BG8" s="36"/>
+      <c r="BH8" s="36"/>
+      <c r="BI8" s="36"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="42"/>
-      <c r="W9" s="42"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="42"/>
-      <c r="Z9" s="42"/>
-      <c r="AA9" s="42"/>
-      <c r="AB9" s="42"/>
-      <c r="AC9" s="42"/>
-      <c r="AD9" s="42"/>
-      <c r="AE9" s="42"/>
-      <c r="AF9" s="42"/>
-      <c r="AG9" s="42"/>
-      <c r="AH9" s="42"/>
-      <c r="AI9" s="42"/>
-      <c r="AJ9" s="42"/>
-      <c r="AK9" s="42"/>
-      <c r="AL9" s="42"/>
-      <c r="AM9" s="42"/>
-      <c r="AN9" s="42"/>
-      <c r="AO9" s="42"/>
-      <c r="AP9" s="42"/>
-      <c r="AQ9" s="42"/>
-      <c r="AR9" s="42"/>
-      <c r="AS9" s="42"/>
-      <c r="AT9" s="42"/>
-      <c r="AU9" s="42"/>
-      <c r="AV9" s="42"/>
-      <c r="AW9" s="42"/>
-      <c r="AX9" s="42"/>
-      <c r="AY9" s="42"/>
-      <c r="AZ9" s="42"/>
-      <c r="BA9" s="42"/>
-      <c r="BB9" s="42"/>
-      <c r="BC9" s="42"/>
-      <c r="BD9" s="42"/>
-      <c r="BE9" s="42"/>
-      <c r="BF9" s="42"/>
-      <c r="BG9" s="42"/>
-      <c r="BH9" s="42"/>
-      <c r="BI9" s="42"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="37"/>
+      <c r="AF9" s="37"/>
+      <c r="AG9" s="37"/>
+      <c r="AH9" s="37"/>
+      <c r="AI9" s="37"/>
+      <c r="AJ9" s="37"/>
+      <c r="AK9" s="37"/>
+      <c r="AL9" s="37"/>
+      <c r="AM9" s="37"/>
+      <c r="AN9" s="37"/>
+      <c r="AO9" s="37"/>
+      <c r="AP9" s="37"/>
+      <c r="AQ9" s="37"/>
+      <c r="AR9" s="37"/>
+      <c r="AS9" s="37"/>
+      <c r="AT9" s="37"/>
+      <c r="AU9" s="37"/>
+      <c r="AV9" s="37"/>
+      <c r="AW9" s="37"/>
+      <c r="AX9" s="37"/>
+      <c r="AY9" s="37"/>
+      <c r="AZ9" s="37"/>
+      <c r="BA9" s="37"/>
+      <c r="BB9" s="37"/>
+      <c r="BC9" s="37"/>
+      <c r="BD9" s="37"/>
+      <c r="BE9" s="37"/>
+      <c r="BF9" s="37"/>
+      <c r="BG9" s="37"/>
+      <c r="BH9" s="37"/>
+      <c r="BI9" s="37"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="42"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="42"/>
-      <c r="AA10" s="42"/>
-      <c r="AB10" s="42"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="42"/>
-      <c r="AE10" s="42"/>
-      <c r="AF10" s="42"/>
-      <c r="AG10" s="42"/>
-      <c r="AH10" s="42"/>
-      <c r="AI10" s="42"/>
-      <c r="AJ10" s="42"/>
-      <c r="AK10" s="42"/>
-      <c r="AL10" s="42"/>
-      <c r="AM10" s="42"/>
-      <c r="AN10" s="42"/>
-      <c r="AO10" s="42"/>
-      <c r="AP10" s="42"/>
-      <c r="AQ10" s="42"/>
-      <c r="AR10" s="42"/>
-      <c r="AS10" s="42"/>
-      <c r="AT10" s="42"/>
-      <c r="AU10" s="42"/>
-      <c r="AV10" s="42"/>
-      <c r="AW10" s="42"/>
-      <c r="AX10" s="42"/>
-      <c r="AY10" s="42"/>
-      <c r="AZ10" s="42"/>
-      <c r="BA10" s="42"/>
-      <c r="BB10" s="42"/>
-      <c r="BC10" s="42"/>
-      <c r="BD10" s="42"/>
-      <c r="BE10" s="42"/>
-      <c r="BF10" s="42"/>
-      <c r="BG10" s="42"/>
-      <c r="BH10" s="42"/>
-      <c r="BI10" s="42"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="37"/>
+      <c r="Z10" s="37"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="37"/>
+      <c r="AC10" s="37"/>
+      <c r="AD10" s="37"/>
+      <c r="AE10" s="37"/>
+      <c r="AF10" s="37"/>
+      <c r="AG10" s="37"/>
+      <c r="AH10" s="37"/>
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="37"/>
+      <c r="AK10" s="37"/>
+      <c r="AL10" s="37"/>
+      <c r="AM10" s="37"/>
+      <c r="AN10" s="37"/>
+      <c r="AO10" s="37"/>
+      <c r="AP10" s="37"/>
+      <c r="AQ10" s="37"/>
+      <c r="AR10" s="37"/>
+      <c r="AS10" s="37"/>
+      <c r="AT10" s="37"/>
+      <c r="AU10" s="37"/>
+      <c r="AV10" s="37"/>
+      <c r="AW10" s="37"/>
+      <c r="AX10" s="37"/>
+      <c r="AY10" s="37"/>
+      <c r="AZ10" s="37"/>
+      <c r="BA10" s="37"/>
+      <c r="BB10" s="37"/>
+      <c r="BC10" s="37"/>
+      <c r="BD10" s="37"/>
+      <c r="BE10" s="37"/>
+      <c r="BF10" s="37"/>
+      <c r="BG10" s="37"/>
+      <c r="BH10" s="37"/>
+      <c r="BI10" s="37"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="42"/>
-      <c r="W11" s="42"/>
-      <c r="X11" s="42"/>
-      <c r="Y11" s="42"/>
-      <c r="Z11" s="42"/>
-      <c r="AA11" s="42"/>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="42"/>
-      <c r="AE11" s="42"/>
-      <c r="AF11" s="42"/>
-      <c r="AG11" s="42"/>
-      <c r="AH11" s="42"/>
-      <c r="AI11" s="42"/>
-      <c r="AJ11" s="42"/>
-      <c r="AK11" s="42"/>
-      <c r="AL11" s="42"/>
-      <c r="AM11" s="42"/>
-      <c r="AN11" s="42"/>
-      <c r="AO11" s="42"/>
-      <c r="AP11" s="42"/>
-      <c r="AQ11" s="42"/>
-      <c r="AR11" s="42"/>
-      <c r="AS11" s="42"/>
-      <c r="AT11" s="42"/>
-      <c r="AU11" s="42"/>
-      <c r="AV11" s="42"/>
-      <c r="AW11" s="42"/>
-      <c r="AX11" s="42"/>
-      <c r="AY11" s="42"/>
-      <c r="AZ11" s="42"/>
-      <c r="BA11" s="42"/>
-      <c r="BB11" s="42"/>
-      <c r="BC11" s="42"/>
-      <c r="BD11" s="42"/>
-      <c r="BE11" s="42"/>
-      <c r="BF11" s="42"/>
-      <c r="BG11" s="42"/>
-      <c r="BH11" s="42"/>
-      <c r="BI11" s="42"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="37"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="37"/>
+      <c r="Z11" s="37"/>
+      <c r="AA11" s="37"/>
+      <c r="AB11" s="37"/>
+      <c r="AC11" s="37"/>
+      <c r="AD11" s="37"/>
+      <c r="AE11" s="37"/>
+      <c r="AF11" s="37"/>
+      <c r="AG11" s="37"/>
+      <c r="AH11" s="37"/>
+      <c r="AI11" s="37"/>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="37"/>
+      <c r="AL11" s="37"/>
+      <c r="AM11" s="37"/>
+      <c r="AN11" s="37"/>
+      <c r="AO11" s="37"/>
+      <c r="AP11" s="37"/>
+      <c r="AQ11" s="37"/>
+      <c r="AR11" s="37"/>
+      <c r="AS11" s="37"/>
+      <c r="AT11" s="37"/>
+      <c r="AU11" s="37"/>
+      <c r="AV11" s="37"/>
+      <c r="AW11" s="37"/>
+      <c r="AX11" s="37"/>
+      <c r="AY11" s="37"/>
+      <c r="AZ11" s="37"/>
+      <c r="BA11" s="37"/>
+      <c r="BB11" s="37"/>
+      <c r="BC11" s="37"/>
+      <c r="BD11" s="37"/>
+      <c r="BE11" s="37"/>
+      <c r="BF11" s="37"/>
+      <c r="BG11" s="37"/>
+      <c r="BH11" s="37"/>
+      <c r="BI11" s="37"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="37"/>
-      <c r="AD13" s="37"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="37"/>
-      <c r="AG13" s="37"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="37"/>
-      <c r="AJ13" s="37"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="37"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="37"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="37"/>
-      <c r="AS13" s="37"/>
-      <c r="AT13" s="37"/>
-      <c r="AU13" s="37"/>
-      <c r="AV13" s="37"/>
-      <c r="AW13" s="37"/>
-      <c r="AX13" s="37"/>
-      <c r="AY13" s="37"/>
-      <c r="AZ13" s="37"/>
-      <c r="BA13" s="37"/>
-      <c r="BB13" s="37"/>
-      <c r="BC13" s="37"/>
-      <c r="BD13" s="37"/>
-      <c r="BE13" s="37"/>
-      <c r="BF13" s="37"/>
-      <c r="BG13" s="37"/>
-      <c r="BH13" s="37"/>
-      <c r="BI13" s="37"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="36"/>
+      <c r="AE13" s="36"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="36"/>
+      <c r="AH13" s="36"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="36"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="36"/>
+      <c r="AN13" s="36"/>
+      <c r="AO13" s="36"/>
+      <c r="AP13" s="36"/>
+      <c r="AQ13" s="36"/>
+      <c r="AR13" s="36"/>
+      <c r="AS13" s="36"/>
+      <c r="AT13" s="36"/>
+      <c r="AU13" s="36"/>
+      <c r="AV13" s="36"/>
+      <c r="AW13" s="36"/>
+      <c r="AX13" s="36"/>
+      <c r="AY13" s="36"/>
+      <c r="AZ13" s="36"/>
+      <c r="BA13" s="36"/>
+      <c r="BB13" s="36"/>
+      <c r="BC13" s="36"/>
+      <c r="BD13" s="36"/>
+      <c r="BE13" s="36"/>
+      <c r="BF13" s="36"/>
+      <c r="BG13" s="36"/>
+      <c r="BH13" s="36"/>
+      <c r="BI13" s="36"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43" t="s">
-        <v>69</v>
+      <c r="A14" s="35" t="s">
+        <v>51</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="43"/>
-      <c r="Y14" s="43"/>
-      <c r="Z14" s="43"/>
-      <c r="AA14" s="43"/>
-      <c r="AB14" s="43"/>
-      <c r="AC14" s="43"/>
-      <c r="AD14" s="43"/>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="43"/>
-      <c r="AG14" s="43"/>
-      <c r="AH14" s="43"/>
-      <c r="AI14" s="43"/>
-      <c r="AJ14" s="43"/>
-      <c r="AK14" s="43"/>
-      <c r="AL14" s="43"/>
-      <c r="AM14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
-      <c r="AQ14" s="43"/>
-      <c r="AR14" s="43"/>
-      <c r="AS14" s="43"/>
-      <c r="AT14" s="43"/>
-      <c r="AU14" s="43"/>
-      <c r="AV14" s="43"/>
-      <c r="AW14" s="43"/>
-      <c r="AX14" s="43"/>
-      <c r="AY14" s="43"/>
-      <c r="AZ14" s="43"/>
-      <c r="BA14" s="43"/>
-      <c r="BB14" s="43"/>
-      <c r="BC14" s="43"/>
-      <c r="BD14" s="43"/>
-      <c r="BE14" s="43"/>
-      <c r="BF14" s="43"/>
-      <c r="BG14" s="43"/>
-      <c r="BH14" s="43"/>
-      <c r="BI14" s="43"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="35"/>
+      <c r="AC14" s="35"/>
+      <c r="AD14" s="35"/>
+      <c r="AE14" s="35"/>
+      <c r="AF14" s="35"/>
+      <c r="AG14" s="35"/>
+      <c r="AH14" s="35"/>
+      <c r="AI14" s="35"/>
+      <c r="AJ14" s="35"/>
+      <c r="AK14" s="35"/>
+      <c r="AL14" s="35"/>
+      <c r="AM14" s="35"/>
+      <c r="AN14" s="35"/>
+      <c r="AO14" s="35"/>
+      <c r="AP14" s="35"/>
+      <c r="AQ14" s="35"/>
+      <c r="AR14" s="35"/>
+      <c r="AS14" s="35"/>
+      <c r="AT14" s="35"/>
+      <c r="AU14" s="35"/>
+      <c r="AV14" s="35"/>
+      <c r="AW14" s="35"/>
+      <c r="AX14" s="35"/>
+      <c r="AY14" s="35"/>
+      <c r="AZ14" s="35"/>
+      <c r="BA14" s="35"/>
+      <c r="BB14" s="35"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="35"/>
+      <c r="BE14" s="35"/>
+      <c r="BF14" s="35"/>
+      <c r="BG14" s="35"/>
+      <c r="BH14" s="35"/>
+      <c r="BI14" s="35"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="43"/>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="43"/>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="43"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="43"/>
-      <c r="AM15" s="43"/>
-      <c r="AN15" s="43"/>
-      <c r="AO15" s="43"/>
-      <c r="AP15" s="43"/>
-      <c r="AQ15" s="43"/>
-      <c r="AR15" s="43"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="43"/>
-      <c r="AU15" s="43"/>
-      <c r="AV15" s="43"/>
-      <c r="AW15" s="43"/>
-      <c r="AX15" s="43"/>
-      <c r="AY15" s="43"/>
-      <c r="AZ15" s="43"/>
-      <c r="BA15" s="43"/>
-      <c r="BB15" s="43"/>
-      <c r="BC15" s="43"/>
-      <c r="BD15" s="43"/>
-      <c r="BE15" s="43"/>
-      <c r="BF15" s="43"/>
-      <c r="BG15" s="43"/>
-      <c r="BH15" s="43"/>
-      <c r="BI15" s="43"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="35"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="35"/>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="35"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="35"/>
+      <c r="AO15" s="35"/>
+      <c r="AP15" s="35"/>
+      <c r="AQ15" s="35"/>
+      <c r="AR15" s="35"/>
+      <c r="AS15" s="35"/>
+      <c r="AT15" s="35"/>
+      <c r="AU15" s="35"/>
+      <c r="AV15" s="35"/>
+      <c r="AW15" s="35"/>
+      <c r="AX15" s="35"/>
+      <c r="AY15" s="35"/>
+      <c r="AZ15" s="35"/>
+      <c r="BA15" s="35"/>
+      <c r="BB15" s="35"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="35"/>
+      <c r="BE15" s="35"/>
+      <c r="BF15" s="35"/>
+      <c r="BG15" s="35"/>
+      <c r="BH15" s="35"/>
+      <c r="BI15" s="35"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="43"/>
-      <c r="AD16" s="43"/>
-      <c r="AE16" s="43"/>
-      <c r="AF16" s="43"/>
-      <c r="AG16" s="43"/>
-      <c r="AH16" s="43"/>
-      <c r="AI16" s="43"/>
-      <c r="AJ16" s="43"/>
-      <c r="AK16" s="43"/>
-      <c r="AL16" s="43"/>
-      <c r="AM16" s="43"/>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="43"/>
-      <c r="AP16" s="43"/>
-      <c r="AQ16" s="43"/>
-      <c r="AR16" s="43"/>
-      <c r="AS16" s="43"/>
-      <c r="AT16" s="43"/>
-      <c r="AU16" s="43"/>
-      <c r="AV16" s="43"/>
-      <c r="AW16" s="43"/>
-      <c r="AX16" s="43"/>
-      <c r="AY16" s="43"/>
-      <c r="AZ16" s="43"/>
-      <c r="BA16" s="43"/>
-      <c r="BB16" s="43"/>
-      <c r="BC16" s="43"/>
-      <c r="BD16" s="43"/>
-      <c r="BE16" s="43"/>
-      <c r="BF16" s="43"/>
-      <c r="BG16" s="43"/>
-      <c r="BH16" s="43"/>
-      <c r="BI16" s="43"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="35"/>
+      <c r="AD16" s="35"/>
+      <c r="AE16" s="35"/>
+      <c r="AF16" s="35"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="35"/>
+      <c r="AJ16" s="35"/>
+      <c r="AK16" s="35"/>
+      <c r="AL16" s="35"/>
+      <c r="AM16" s="35"/>
+      <c r="AN16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="35"/>
+      <c r="AQ16" s="35"/>
+      <c r="AR16" s="35"/>
+      <c r="AS16" s="35"/>
+      <c r="AT16" s="35"/>
+      <c r="AU16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16" s="35"/>
+      <c r="AX16" s="35"/>
+      <c r="AY16" s="35"/>
+      <c r="AZ16" s="35"/>
+      <c r="BA16" s="35"/>
+      <c r="BB16" s="35"/>
+      <c r="BC16" s="35"/>
+      <c r="BD16" s="35"/>
+      <c r="BE16" s="35"/>
+      <c r="BF16" s="35"/>
+      <c r="BG16" s="35"/>
+      <c r="BH16" s="35"/>
+      <c r="BI16" s="35"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="43"/>
-      <c r="Y17" s="43"/>
-      <c r="Z17" s="43"/>
-      <c r="AA17" s="43"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="43"/>
-      <c r="AD17" s="43"/>
-      <c r="AE17" s="43"/>
-      <c r="AF17" s="43"/>
-      <c r="AG17" s="43"/>
-      <c r="AH17" s="43"/>
-      <c r="AI17" s="43"/>
-      <c r="AJ17" s="43"/>
-      <c r="AK17" s="43"/>
-      <c r="AL17" s="43"/>
-      <c r="AM17" s="43"/>
-      <c r="AN17" s="43"/>
-      <c r="AO17" s="43"/>
-      <c r="AP17" s="43"/>
-      <c r="AQ17" s="43"/>
-      <c r="AR17" s="43"/>
-      <c r="AS17" s="43"/>
-      <c r="AT17" s="43"/>
-      <c r="AU17" s="43"/>
-      <c r="AV17" s="43"/>
-      <c r="AW17" s="43"/>
-      <c r="AX17" s="43"/>
-      <c r="AY17" s="43"/>
-      <c r="AZ17" s="43"/>
-      <c r="BA17" s="43"/>
-      <c r="BB17" s="43"/>
-      <c r="BC17" s="43"/>
-      <c r="BD17" s="43"/>
-      <c r="BE17" s="43"/>
-      <c r="BF17" s="43"/>
-      <c r="BG17" s="43"/>
-      <c r="BH17" s="43"/>
-      <c r="BI17" s="43"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="35"/>
+      <c r="AD17" s="35"/>
+      <c r="AE17" s="35"/>
+      <c r="AF17" s="35"/>
+      <c r="AG17" s="35"/>
+      <c r="AH17" s="35"/>
+      <c r="AI17" s="35"/>
+      <c r="AJ17" s="35"/>
+      <c r="AK17" s="35"/>
+      <c r="AL17" s="35"/>
+      <c r="AM17" s="35"/>
+      <c r="AN17" s="35"/>
+      <c r="AO17" s="35"/>
+      <c r="AP17" s="35"/>
+      <c r="AQ17" s="35"/>
+      <c r="AR17" s="35"/>
+      <c r="AS17" s="35"/>
+      <c r="AT17" s="35"/>
+      <c r="AU17" s="35"/>
+      <c r="AV17" s="35"/>
+      <c r="AW17" s="35"/>
+      <c r="AX17" s="35"/>
+      <c r="AY17" s="35"/>
+      <c r="AZ17" s="35"/>
+      <c r="BA17" s="35"/>
+      <c r="BB17" s="35"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="35"/>
+      <c r="BE17" s="35"/>
+      <c r="BF17" s="35"/>
+      <c r="BG17" s="35"/>
+      <c r="BH17" s="35"/>
+      <c r="BI17" s="35"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="43"/>
-      <c r="Y18" s="43"/>
-      <c r="Z18" s="43"/>
-      <c r="AA18" s="43"/>
-      <c r="AB18" s="43"/>
-      <c r="AC18" s="43"/>
-      <c r="AD18" s="43"/>
-      <c r="AE18" s="43"/>
-      <c r="AF18" s="43"/>
-      <c r="AG18" s="43"/>
-      <c r="AH18" s="43"/>
-      <c r="AI18" s="43"/>
-      <c r="AJ18" s="43"/>
-      <c r="AK18" s="43"/>
-      <c r="AL18" s="43"/>
-      <c r="AM18" s="43"/>
-      <c r="AN18" s="43"/>
-      <c r="AO18" s="43"/>
-      <c r="AP18" s="43"/>
-      <c r="AQ18" s="43"/>
-      <c r="AR18" s="43"/>
-      <c r="AS18" s="43"/>
-      <c r="AT18" s="43"/>
-      <c r="AU18" s="43"/>
-      <c r="AV18" s="43"/>
-      <c r="AW18" s="43"/>
-      <c r="AX18" s="43"/>
-      <c r="AY18" s="43"/>
-      <c r="AZ18" s="43"/>
-      <c r="BA18" s="43"/>
-      <c r="BB18" s="43"/>
-      <c r="BC18" s="43"/>
-      <c r="BD18" s="43"/>
-      <c r="BE18" s="43"/>
-      <c r="BF18" s="43"/>
-      <c r="BG18" s="43"/>
-      <c r="BH18" s="43"/>
-      <c r="BI18" s="43"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="35"/>
+      <c r="AC18" s="35"/>
+      <c r="AD18" s="35"/>
+      <c r="AE18" s="35"/>
+      <c r="AF18" s="35"/>
+      <c r="AG18" s="35"/>
+      <c r="AH18" s="35"/>
+      <c r="AI18" s="35"/>
+      <c r="AJ18" s="35"/>
+      <c r="AK18" s="35"/>
+      <c r="AL18" s="35"/>
+      <c r="AM18" s="35"/>
+      <c r="AN18" s="35"/>
+      <c r="AO18" s="35"/>
+      <c r="AP18" s="35"/>
+      <c r="AQ18" s="35"/>
+      <c r="AR18" s="35"/>
+      <c r="AS18" s="35"/>
+      <c r="AT18" s="35"/>
+      <c r="AU18" s="35"/>
+      <c r="AV18" s="35"/>
+      <c r="AW18" s="35"/>
+      <c r="AX18" s="35"/>
+      <c r="AY18" s="35"/>
+      <c r="AZ18" s="35"/>
+      <c r="BA18" s="35"/>
+      <c r="BB18" s="35"/>
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="35"/>
+      <c r="BE18" s="35"/>
+      <c r="BF18" s="35"/>
+      <c r="BG18" s="35"/>
+      <c r="BH18" s="35"/>
+      <c r="BI18" s="35"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="43"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="43"/>
-      <c r="AD19" s="43"/>
-      <c r="AE19" s="43"/>
-      <c r="AF19" s="43"/>
-      <c r="AG19" s="43"/>
-      <c r="AH19" s="43"/>
-      <c r="AI19" s="43"/>
-      <c r="AJ19" s="43"/>
-      <c r="AK19" s="43"/>
-      <c r="AL19" s="43"/>
-      <c r="AM19" s="43"/>
-      <c r="AN19" s="43"/>
-      <c r="AO19" s="43"/>
-      <c r="AP19" s="43"/>
-      <c r="AQ19" s="43"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
-      <c r="AT19" s="43"/>
-      <c r="AU19" s="43"/>
-      <c r="AV19" s="43"/>
-      <c r="AW19" s="43"/>
-      <c r="AX19" s="43"/>
-      <c r="AY19" s="43"/>
-      <c r="AZ19" s="43"/>
-      <c r="BA19" s="43"/>
-      <c r="BB19" s="43"/>
-      <c r="BC19" s="43"/>
-      <c r="BD19" s="43"/>
-      <c r="BE19" s="43"/>
-      <c r="BF19" s="43"/>
-      <c r="BG19" s="43"/>
-      <c r="BH19" s="43"/>
-      <c r="BI19" s="43"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="35"/>
+      <c r="AE19" s="35"/>
+      <c r="AF19" s="35"/>
+      <c r="AG19" s="35"/>
+      <c r="AH19" s="35"/>
+      <c r="AI19" s="35"/>
+      <c r="AJ19" s="35"/>
+      <c r="AK19" s="35"/>
+      <c r="AL19" s="35"/>
+      <c r="AM19" s="35"/>
+      <c r="AN19" s="35"/>
+      <c r="AO19" s="35"/>
+      <c r="AP19" s="35"/>
+      <c r="AQ19" s="35"/>
+      <c r="AR19" s="35"/>
+      <c r="AS19" s="35"/>
+      <c r="AT19" s="35"/>
+      <c r="AU19" s="35"/>
+      <c r="AV19" s="35"/>
+      <c r="AW19" s="35"/>
+      <c r="AX19" s="35"/>
+      <c r="AY19" s="35"/>
+      <c r="AZ19" s="35"/>
+      <c r="BA19" s="35"/>
+      <c r="BB19" s="35"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="35"/>
+      <c r="BE19" s="35"/>
+      <c r="BF19" s="35"/>
+      <c r="BG19" s="35"/>
+      <c r="BH19" s="35"/>
+      <c r="BI19" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A14:BI19"/>
-    <mergeCell ref="A13:BI13"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:T10"/>
-    <mergeCell ref="U10:AD10"/>
-    <mergeCell ref="AE10:AN10"/>
-    <mergeCell ref="AO10:BI10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:T11"/>
-    <mergeCell ref="U11:AD11"/>
-    <mergeCell ref="AE11:AN11"/>
-    <mergeCell ref="AO11:BI11"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:T9"/>
-    <mergeCell ref="U9:AD9"/>
-    <mergeCell ref="AE9:AN9"/>
-    <mergeCell ref="AO9:BI9"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
@@ -2918,14 +2911,29 @@
     <mergeCell ref="R2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="K9:T9"/>
+    <mergeCell ref="U9:AD9"/>
+    <mergeCell ref="AE9:AN9"/>
+    <mergeCell ref="AO9:BI9"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
+    <mergeCell ref="A14:BI19"/>
+    <mergeCell ref="A13:BI13"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:AD10"/>
+    <mergeCell ref="AE10:AN10"/>
+    <mergeCell ref="AO10:BI10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="U11:AD11"/>
+    <mergeCell ref="AE11:AN11"/>
+    <mergeCell ref="AO11:BI11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2937,93 +2945,93 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IX52"/>
+  <dimension ref="A1:IX54"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="32" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="33" t="s">
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="32" t="s">
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="33" t="str">
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44"/>
+      <c r="AE1" s="43" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="33"/>
-      <c r="AN1" s="33"/>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="32" t="s">
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="43"/>
+      <c r="AK1" s="43"/>
+      <c r="AL1" s="43"/>
+      <c r="AM1" s="43"/>
+      <c r="AN1" s="43"/>
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="43"/>
+      <c r="AQ1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="33" t="s">
+      <c r="AR1" s="44"/>
+      <c r="AS1" s="44"/>
+      <c r="AT1" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="33"/>
-      <c r="AV1" s="33"/>
-      <c r="AW1" s="33"/>
-      <c r="AX1" s="33"/>
-      <c r="AY1" s="33"/>
-      <c r="AZ1" s="33"/>
-      <c r="BA1" s="32" t="s">
+      <c r="AU1" s="43"/>
+      <c r="AV1" s="43"/>
+      <c r="AW1" s="43"/>
+      <c r="AX1" s="43"/>
+      <c r="AY1" s="43"/>
+      <c r="AZ1" s="43"/>
+      <c r="BA1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-      <c r="BD1" s="40">
+      <c r="BB1" s="44"/>
+      <c r="BC1" s="44"/>
+      <c r="BD1" s="45">
         <v>45555</v>
       </c>
-      <c r="BE1" s="40"/>
-      <c r="BF1" s="40"/>
-      <c r="BG1" s="40"/>
-      <c r="BH1" s="40"/>
-      <c r="BI1" s="40"/>
+      <c r="BE1" s="45"/>
+      <c r="BF1" s="45"/>
+      <c r="BG1" s="45"/>
+      <c r="BH1" s="45"/>
+      <c r="BI1" s="45"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3223,82 +3231,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="32" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="32" t="s">
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="33" t="str">
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="43" t="str">
         <f>クラス仕様!G5</f>
         <v>PagingUtil</v>
       </c>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="33"/>
-      <c r="AN2" s="33"/>
-      <c r="AO2" s="33"/>
-      <c r="AP2" s="33"/>
-      <c r="AQ2" s="32" t="s">
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="33" t="s">
-        <v>68</v>
+      <c r="AR2" s="44"/>
+      <c r="AS2" s="44"/>
+      <c r="AT2" s="43" t="s">
+        <v>50</v>
       </c>
-      <c r="AU2" s="33"/>
-      <c r="AV2" s="33"/>
-      <c r="AW2" s="33"/>
-      <c r="AX2" s="33"/>
-      <c r="AY2" s="33"/>
-      <c r="AZ2" s="33"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="43"/>
+      <c r="AX2" s="43"/>
+      <c r="AY2" s="43"/>
+      <c r="AZ2" s="43"/>
+      <c r="BA2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="34">
-        <v>45566</v>
+      <c r="BB2" s="44"/>
+      <c r="BC2" s="44"/>
+      <c r="BD2" s="39">
+        <v>45587</v>
       </c>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="36"/>
+      <c r="BE2" s="40"/>
+      <c r="BF2" s="40"/>
+      <c r="BG2" s="40"/>
+      <c r="BH2" s="40"/>
+      <c r="BI2" s="41"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3561,16 +3569,16 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="38" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
@@ -3825,14 +3833,14 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
       <c r="G5" s="38" t="s">
         <v>33</v>
       </c>
@@ -4349,75 +4357,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47" t="s">
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
-      <c r="AA7" s="47"/>
-      <c r="AB7" s="47"/>
-      <c r="AC7" s="47"/>
-      <c r="AD7" s="47"/>
-      <c r="AE7" s="47" t="s">
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="49"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="49"/>
+      <c r="AE7" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="47"/>
-      <c r="AG7" s="47"/>
-      <c r="AH7" s="47"/>
-      <c r="AI7" s="47"/>
-      <c r="AJ7" s="47"/>
-      <c r="AK7" s="47"/>
-      <c r="AL7" s="47"/>
-      <c r="AM7" s="47"/>
-      <c r="AN7" s="47"/>
-      <c r="AO7" s="47"/>
-      <c r="AP7" s="47"/>
-      <c r="AQ7" s="47"/>
-      <c r="AR7" s="47"/>
-      <c r="AS7" s="47"/>
-      <c r="AT7" s="47"/>
-      <c r="AU7" s="47"/>
-      <c r="AV7" s="47"/>
-      <c r="AW7" s="47"/>
-      <c r="AX7" s="47"/>
-      <c r="AY7" s="47"/>
-      <c r="AZ7" s="47"/>
-      <c r="BA7" s="47"/>
-      <c r="BB7" s="47"/>
-      <c r="BC7" s="47"/>
-      <c r="BD7" s="47"/>
-      <c r="BE7" s="47"/>
-      <c r="BF7" s="47"/>
-      <c r="BG7" s="47"/>
-      <c r="BH7" s="47"/>
-      <c r="BI7" s="47"/>
+      <c r="AF7" s="49"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
+      <c r="AL7" s="49"/>
+      <c r="AM7" s="49"/>
+      <c r="AN7" s="49"/>
+      <c r="AO7" s="49"/>
+      <c r="AP7" s="49"/>
+      <c r="AQ7" s="49"/>
+      <c r="AR7" s="49"/>
+      <c r="AS7" s="49"/>
+      <c r="AT7" s="49"/>
+      <c r="AU7" s="49"/>
+      <c r="AV7" s="49"/>
+      <c r="AW7" s="49"/>
+      <c r="AX7" s="49"/>
+      <c r="AY7" s="49"/>
+      <c r="AZ7" s="49"/>
+      <c r="BA7" s="49"/>
+      <c r="BB7" s="49"/>
+      <c r="BC7" s="49"/>
+      <c r="BD7" s="49"/>
+      <c r="BE7" s="49"/>
+      <c r="BF7" s="49"/>
+      <c r="BG7" s="49"/>
+      <c r="BH7" s="49"/>
+      <c r="BI7" s="49"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4617,75 +4625,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="44" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="44" t="s">
-        <v>66</v>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="53" t="s">
+        <v>48</v>
       </c>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="45"/>
-      <c r="AA8" s="45"/>
-      <c r="AB8" s="45"/>
-      <c r="AC8" s="45"/>
-      <c r="AD8" s="46"/>
-      <c r="AE8" s="44" t="s">
-        <v>72</v>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="54"/>
+      <c r="AD8" s="55"/>
+      <c r="AE8" s="53" t="s">
+        <v>54</v>
       </c>
-      <c r="AF8" s="45"/>
-      <c r="AG8" s="45"/>
-      <c r="AH8" s="45"/>
-      <c r="AI8" s="45"/>
-      <c r="AJ8" s="45"/>
-      <c r="AK8" s="45"/>
-      <c r="AL8" s="45"/>
-      <c r="AM8" s="45"/>
-      <c r="AN8" s="45"/>
-      <c r="AO8" s="45"/>
-      <c r="AP8" s="45"/>
-      <c r="AQ8" s="45"/>
-      <c r="AR8" s="45"/>
-      <c r="AS8" s="45"/>
-      <c r="AT8" s="45"/>
-      <c r="AU8" s="45"/>
-      <c r="AV8" s="45"/>
-      <c r="AW8" s="45"/>
-      <c r="AX8" s="45"/>
-      <c r="AY8" s="45"/>
-      <c r="AZ8" s="45"/>
-      <c r="BA8" s="45"/>
-      <c r="BB8" s="45"/>
-      <c r="BC8" s="45"/>
-      <c r="BD8" s="45"/>
-      <c r="BE8" s="45"/>
-      <c r="BF8" s="45"/>
-      <c r="BG8" s="45"/>
-      <c r="BH8" s="45"/>
-      <c r="BI8" s="46"/>
+      <c r="AF8" s="54"/>
+      <c r="AG8" s="54"/>
+      <c r="AH8" s="54"/>
+      <c r="AI8" s="54"/>
+      <c r="AJ8" s="54"/>
+      <c r="AK8" s="54"/>
+      <c r="AL8" s="54"/>
+      <c r="AM8" s="54"/>
+      <c r="AN8" s="54"/>
+      <c r="AO8" s="54"/>
+      <c r="AP8" s="54"/>
+      <c r="AQ8" s="54"/>
+      <c r="AR8" s="54"/>
+      <c r="AS8" s="54"/>
+      <c r="AT8" s="54"/>
+      <c r="AU8" s="54"/>
+      <c r="AV8" s="54"/>
+      <c r="AW8" s="54"/>
+      <c r="AX8" s="54"/>
+      <c r="AY8" s="54"/>
+      <c r="AZ8" s="54"/>
+      <c r="BA8" s="54"/>
+      <c r="BB8" s="54"/>
+      <c r="BC8" s="54"/>
+      <c r="BD8" s="54"/>
+      <c r="BE8" s="54"/>
+      <c r="BF8" s="54"/>
+      <c r="BG8" s="54"/>
+      <c r="BH8" s="54"/>
+      <c r="BI8" s="55"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -4885,75 +4893,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49" t="s">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="49" t="s">
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="49" t="s">
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="48"/>
+      <c r="AA9" s="48"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="49"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
-      <c r="AL9" s="49"/>
-      <c r="AM9" s="49"/>
-      <c r="AN9" s="49"/>
-      <c r="AO9" s="49"/>
-      <c r="AP9" s="49"/>
-      <c r="AQ9" s="49"/>
-      <c r="AR9" s="49"/>
-      <c r="AS9" s="49"/>
-      <c r="AT9" s="49"/>
-      <c r="AU9" s="49"/>
-      <c r="AV9" s="49"/>
-      <c r="AW9" s="49"/>
-      <c r="AX9" s="49"/>
-      <c r="AY9" s="49"/>
-      <c r="AZ9" s="49"/>
-      <c r="BA9" s="49"/>
-      <c r="BB9" s="49"/>
-      <c r="BC9" s="49"/>
-      <c r="BD9" s="49"/>
-      <c r="BE9" s="49"/>
-      <c r="BF9" s="49"/>
-      <c r="BG9" s="49"/>
-      <c r="BH9" s="49"/>
-      <c r="BI9" s="49"/>
+      <c r="AF9" s="48"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="48"/>
+      <c r="AI9" s="48"/>
+      <c r="AJ9" s="48"/>
+      <c r="AK9" s="48"/>
+      <c r="AL9" s="48"/>
+      <c r="AM9" s="48"/>
+      <c r="AN9" s="48"/>
+      <c r="AO9" s="48"/>
+      <c r="AP9" s="48"/>
+      <c r="AQ9" s="48"/>
+      <c r="AR9" s="48"/>
+      <c r="AS9" s="48"/>
+      <c r="AT9" s="48"/>
+      <c r="AU9" s="48"/>
+      <c r="AV9" s="48"/>
+      <c r="AW9" s="48"/>
+      <c r="AX9" s="48"/>
+      <c r="AY9" s="48"/>
+      <c r="AZ9" s="48"/>
+      <c r="BA9" s="48"/>
+      <c r="BB9" s="48"/>
+      <c r="BC9" s="48"/>
+      <c r="BD9" s="48"/>
+      <c r="BE9" s="48"/>
+      <c r="BF9" s="48"/>
+      <c r="BG9" s="48"/>
+      <c r="BH9" s="48"/>
+      <c r="BI9" s="48"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -5153,71 +5161,71 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
-        <v>73</v>
+      <c r="A10" s="37" t="s">
+        <v>55</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="52" t="s">
-        <v>74</v>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="50" t="s">
+        <v>56</v>
       </c>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="53"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="53"/>
-      <c r="AB10" s="53"/>
-      <c r="AC10" s="53"/>
-      <c r="AD10" s="53"/>
-      <c r="AE10" s="53"/>
-      <c r="AF10" s="53"/>
-      <c r="AG10" s="53"/>
-      <c r="AH10" s="53"/>
-      <c r="AI10" s="53"/>
-      <c r="AJ10" s="53"/>
-      <c r="AK10" s="53"/>
-      <c r="AL10" s="53"/>
-      <c r="AM10" s="53"/>
-      <c r="AN10" s="53"/>
-      <c r="AO10" s="53"/>
-      <c r="AP10" s="53"/>
-      <c r="AQ10" s="53"/>
-      <c r="AR10" s="53"/>
-      <c r="AS10" s="53"/>
-      <c r="AT10" s="53"/>
-      <c r="AU10" s="53"/>
-      <c r="AV10" s="53"/>
-      <c r="AW10" s="53"/>
-      <c r="AX10" s="53"/>
-      <c r="AY10" s="53"/>
-      <c r="AZ10" s="53"/>
-      <c r="BA10" s="53"/>
-      <c r="BB10" s="53"/>
-      <c r="BC10" s="53"/>
-      <c r="BD10" s="53"/>
-      <c r="BE10" s="53"/>
-      <c r="BF10" s="53"/>
-      <c r="BG10" s="53"/>
-      <c r="BH10" s="53"/>
-      <c r="BI10" s="54"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="51"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="51"/>
+      <c r="X10" s="51"/>
+      <c r="Y10" s="51"/>
+      <c r="Z10" s="51"/>
+      <c r="AA10" s="51"/>
+      <c r="AB10" s="51"/>
+      <c r="AC10" s="51"/>
+      <c r="AD10" s="51"/>
+      <c r="AE10" s="51"/>
+      <c r="AF10" s="51"/>
+      <c r="AG10" s="51"/>
+      <c r="AH10" s="51"/>
+      <c r="AI10" s="51"/>
+      <c r="AJ10" s="51"/>
+      <c r="AK10" s="51"/>
+      <c r="AL10" s="51"/>
+      <c r="AM10" s="51"/>
+      <c r="AN10" s="51"/>
+      <c r="AO10" s="51"/>
+      <c r="AP10" s="51"/>
+      <c r="AQ10" s="51"/>
+      <c r="AR10" s="51"/>
+      <c r="AS10" s="51"/>
+      <c r="AT10" s="51"/>
+      <c r="AU10" s="51"/>
+      <c r="AV10" s="51"/>
+      <c r="AW10" s="51"/>
+      <c r="AX10" s="51"/>
+      <c r="AY10" s="51"/>
+      <c r="AZ10" s="51"/>
+      <c r="BA10" s="51"/>
+      <c r="BB10" s="51"/>
+      <c r="BC10" s="51"/>
+      <c r="BD10" s="51"/>
+      <c r="BE10" s="51"/>
+      <c r="BF10" s="51"/>
+      <c r="BG10" s="51"/>
+      <c r="BH10" s="51"/>
+      <c r="BI10" s="52"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5677,73 +5685,73 @@
       <c r="IX11" s="1"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47" t="s">
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="47"/>
-      <c r="AC12" s="47"/>
-      <c r="AD12" s="47"/>
-      <c r="AE12" s="47"/>
-      <c r="AF12" s="47"/>
-      <c r="AG12" s="47"/>
-      <c r="AH12" s="47"/>
-      <c r="AI12" s="47"/>
-      <c r="AJ12" s="47"/>
-      <c r="AK12" s="47"/>
-      <c r="AL12" s="47"/>
-      <c r="AM12" s="47"/>
-      <c r="AN12" s="47"/>
-      <c r="AO12" s="47"/>
-      <c r="AP12" s="47"/>
-      <c r="AQ12" s="47"/>
-      <c r="AR12" s="47"/>
-      <c r="AS12" s="47"/>
-      <c r="AT12" s="47" t="s">
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="49"/>
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="49"/>
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="49"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
+      <c r="AP12" s="49"/>
+      <c r="AQ12" s="49"/>
+      <c r="AR12" s="49"/>
+      <c r="AS12" s="49"/>
+      <c r="AT12" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="AU12" s="47"/>
-      <c r="AV12" s="47"/>
-      <c r="AW12" s="47"/>
-      <c r="AX12" s="47"/>
-      <c r="AY12" s="47"/>
-      <c r="AZ12" s="47"/>
-      <c r="BA12" s="47"/>
-      <c r="BB12" s="47"/>
-      <c r="BC12" s="47"/>
-      <c r="BD12" s="47"/>
-      <c r="BE12" s="47"/>
-      <c r="BF12" s="47"/>
-      <c r="BG12" s="47"/>
-      <c r="BH12" s="47"/>
-      <c r="BI12" s="47"/>
+      <c r="AU12" s="49"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
+      <c r="BB12" s="49"/>
+      <c r="BC12" s="49"/>
+      <c r="BD12" s="49"/>
+      <c r="BE12" s="49"/>
+      <c r="BF12" s="49"/>
+      <c r="BG12" s="49"/>
+      <c r="BH12" s="49"/>
+      <c r="BI12" s="49"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
@@ -5943,9 +5951,7 @@
       <c r="IX12" s="1"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -5960,7 +5966,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="50" t="s">
+      <c r="P13" s="32" t="s">
         <v>37</v>
       </c>
       <c r="Q13" s="14"/>
@@ -6207,7 +6213,9 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -6222,10 +6230,10 @@
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="51" t="s">
-        <v>38</v>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="2" t="s">
+        <v>62</v>
       </c>
-      <c r="Q14" s="17"/>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
       <c r="T14" s="17"/>
@@ -6484,10 +6492,10 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="11"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="17" t="s">
-        <v>76</v>
+      <c r="P15" s="33" t="s">
+        <v>38</v>
       </c>
+      <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
@@ -6731,9 +6739,7 @@
       <c r="IX15" s="1"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="A16" s="8"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -6748,9 +6754,9 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="11"/>
-      <c r="P16" s="51"/>
+      <c r="P16" s="33"/>
       <c r="Q16" s="17" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
@@ -6995,7 +7001,9 @@
       <c r="IX16" s="1"/>
     </row>
     <row r="17" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -7010,9 +7018,9 @@
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="51"/>
+      <c r="P17" s="33"/>
       <c r="Q17" s="17" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
@@ -7257,9 +7265,7 @@
       <c r="IX17" s="1"/>
     </row>
     <row r="18" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="A18" s="8"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -7274,9 +7280,9 @@
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="11"/>
-      <c r="P18" s="51"/>
+      <c r="P18" s="33"/>
       <c r="Q18" s="17" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
@@ -7521,7 +7527,9 @@
       <c r="IX18" s="1"/>
     </row>
     <row r="19" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -7536,9 +7544,9 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="11"/>
-      <c r="P19" s="16"/>
+      <c r="P19" s="33"/>
       <c r="Q19" s="17" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
@@ -7784,7 +7792,8 @@
     </row>
     <row r="20" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -7797,12 +7806,12 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="11"/>
-      <c r="P20" s="51" t="s">
-        <v>40</v>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="17" t="s">
+        <v>59</v>
       </c>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
       <c r="V20" s="17"/>
@@ -7830,7 +7839,7 @@
       <c r="AR20" s="17"/>
       <c r="AS20" s="18"/>
       <c r="AT20" s="8"/>
-      <c r="AU20" s="9"/>
+      <c r="AU20" s="10"/>
       <c r="AV20" s="10"/>
       <c r="AW20" s="10"/>
       <c r="AX20" s="10"/>
@@ -8045,7 +8054,8 @@
     </row>
     <row r="21" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -8058,12 +8068,12 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
       <c r="O21" s="11"/>
-      <c r="P21" s="51" t="s">
-        <v>81</v>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="17" t="s">
+        <v>67</v>
       </c>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
       <c r="T21" s="17"/>
       <c r="U21" s="17"/>
       <c r="V21" s="17"/>
@@ -8091,7 +8101,7 @@
       <c r="AR21" s="17"/>
       <c r="AS21" s="18"/>
       <c r="AT21" s="8"/>
-      <c r="AU21" s="9"/>
+      <c r="AU21" s="10"/>
       <c r="AV21" s="10"/>
       <c r="AW21" s="10"/>
       <c r="AX21" s="10"/>
@@ -8319,10 +8329,10 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
       <c r="O22" s="11"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="19" t="s">
-        <v>42</v>
+      <c r="P22" s="33" t="s">
+        <v>40</v>
       </c>
+      <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
       <c r="T22" s="17"/>
@@ -8580,11 +8590,11 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
       <c r="O23" s="11"/>
-      <c r="P23" s="16"/>
+      <c r="P23" s="33" t="s">
+        <v>60</v>
+      </c>
       <c r="Q23" s="19"/>
-      <c r="R23" s="19" t="s">
-        <v>50</v>
-      </c>
+      <c r="R23" s="19"/>
       <c r="S23" s="19"/>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
@@ -8843,7 +8853,7 @@
       <c r="O24" s="11"/>
       <c r="P24" s="16"/>
       <c r="Q24" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R24" s="19"/>
       <c r="S24" s="19"/>
@@ -9103,10 +9113,10 @@
       <c r="N25" s="10"/>
       <c r="O25" s="11"/>
       <c r="P25" s="16"/>
-      <c r="Q25" s="19" t="s">
-        <v>44</v>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19" t="s">
+        <v>68</v>
       </c>
-      <c r="R25" s="19"/>
       <c r="S25" s="19"/>
       <c r="T25" s="17"/>
       <c r="U25" s="17"/>
@@ -9365,7 +9375,7 @@
       <c r="O26" s="11"/>
       <c r="P26" s="16"/>
       <c r="Q26" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
@@ -9625,10 +9635,10 @@
       <c r="N27" s="10"/>
       <c r="O27" s="11"/>
       <c r="P27" s="16"/>
-      <c r="Q27" s="19" t="s">
-        <v>45</v>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19" t="s">
+        <v>85</v>
       </c>
-      <c r="R27" s="19"/>
       <c r="S27" s="19"/>
       <c r="T27" s="17"/>
       <c r="U27" s="17"/>
@@ -9886,10 +9896,10 @@
       <c r="N28" s="10"/>
       <c r="O28" s="11"/>
       <c r="P28" s="16"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19" t="s">
-        <v>46</v>
+      <c r="Q28" s="19" t="s">
+        <v>74</v>
       </c>
+      <c r="R28" s="19"/>
       <c r="S28" s="19"/>
       <c r="T28" s="17"/>
       <c r="U28" s="17"/>
@@ -10132,9 +10142,7 @@
       <c r="IX28" s="1"/>
     </row>
     <row r="29" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -10149,14 +10157,14 @@
       <c r="N29" s="10"/>
       <c r="O29" s="11"/>
       <c r="P29" s="16"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17" t="s">
-        <v>47</v>
+      <c r="Q29" s="19" t="s">
+        <v>69</v>
       </c>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
       <c r="T29" s="17"/>
       <c r="U29" s="17"/>
-      <c r="V29" s="19"/>
+      <c r="V29" s="17"/>
       <c r="W29" s="17"/>
       <c r="X29" s="17"/>
       <c r="Y29" s="17"/>
@@ -10397,10 +10405,9 @@
     <row r="30" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
@@ -10411,11 +10418,11 @@
       <c r="N30" s="10"/>
       <c r="O30" s="11"/>
       <c r="P30" s="16"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17" t="s">
-        <v>48</v>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19" t="s">
+        <v>70</v>
       </c>
-      <c r="S30" s="17"/>
+      <c r="S30" s="19"/>
       <c r="T30" s="17"/>
       <c r="U30" s="17"/>
       <c r="V30" s="17"/>
@@ -10443,7 +10450,7 @@
       <c r="AR30" s="17"/>
       <c r="AS30" s="18"/>
       <c r="AT30" s="8"/>
-      <c r="AU30" s="10"/>
+      <c r="AU30" s="9"/>
       <c r="AV30" s="10"/>
       <c r="AW30" s="10"/>
       <c r="AX30" s="10"/>
@@ -10657,9 +10664,10 @@
       <c r="IX30" s="1"/>
     </row>
     <row r="31" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
+      <c r="A31" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="B31" s="9"/>
-      <c r="C31" s="10"/>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -10672,15 +10680,15 @@
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
       <c r="O31" s="11"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19" t="s">
-        <v>49</v>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17" t="s">
+        <v>43</v>
       </c>
-      <c r="T31" s="19"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="22"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="19"/>
       <c r="W31" s="17"/>
       <c r="X31" s="17"/>
       <c r="Y31" s="17"/>
@@ -10705,7 +10713,7 @@
       <c r="AR31" s="17"/>
       <c r="AS31" s="18"/>
       <c r="AT31" s="8"/>
-      <c r="AU31" s="10"/>
+      <c r="AU31" s="9"/>
       <c r="AV31" s="10"/>
       <c r="AW31" s="10"/>
       <c r="AX31" s="10"/>
@@ -10922,9 +10930,9 @@
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
@@ -10934,15 +10942,15 @@
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="11"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19" t="s">
-        <v>51</v>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17" t="s">
+        <v>71</v>
       </c>
-      <c r="T32" s="19"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
       <c r="W32" s="17"/>
       <c r="X32" s="17"/>
       <c r="Y32" s="17"/>
@@ -11198,13 +11206,13 @@
       <c r="O33" s="11"/>
       <c r="P33" s="20"/>
       <c r="Q33" s="21"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17" t="s">
-        <v>52</v>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19" t="s">
+        <v>44</v>
       </c>
-      <c r="T33" s="17"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="22"/>
       <c r="W33" s="17"/>
       <c r="X33" s="17"/>
       <c r="Y33" s="17"/>
@@ -11460,13 +11468,13 @@
       <c r="O34" s="11"/>
       <c r="P34" s="20"/>
       <c r="Q34" s="21"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17" t="s">
-        <v>53</v>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19" t="s">
+        <v>75</v>
       </c>
-      <c r="T34" s="17"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
       <c r="W34" s="17"/>
       <c r="X34" s="17"/>
       <c r="Y34" s="17"/>
@@ -11705,9 +11713,7 @@
       <c r="IX34" s="1"/>
     </row>
     <row r="35" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -11724,13 +11730,13 @@
       <c r="O35" s="11"/>
       <c r="P35" s="20"/>
       <c r="Q35" s="21"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19" t="s">
-        <v>54</v>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17" t="s">
+        <v>79</v>
       </c>
-      <c r="T35" s="19"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="19"/>
+      <c r="V35" s="19"/>
       <c r="W35" s="17"/>
       <c r="X35" s="17"/>
       <c r="Y35" s="17"/>
@@ -11986,13 +11992,13 @@
       <c r="O36" s="11"/>
       <c r="P36" s="20"/>
       <c r="Q36" s="21"/>
-      <c r="R36" s="19" t="s">
-        <v>55</v>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17" t="s">
+        <v>45</v>
       </c>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="19"/>
+      <c r="V36" s="19"/>
       <c r="W36" s="17"/>
       <c r="X36" s="17"/>
       <c r="Y36" s="17"/>
@@ -12231,7 +12237,9 @@
       <c r="IX36" s="1"/>
     </row>
     <row r="37" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
+      <c r="A37" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="B37" s="9"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -12248,13 +12256,13 @@
       <c r="O37" s="11"/>
       <c r="P37" s="20"/>
       <c r="Q37" s="21"/>
-      <c r="R37" s="17"/>
+      <c r="R37" s="19"/>
       <c r="S37" s="19" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
-      <c r="T37" s="17"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="19"/>
+      <c r="T37" s="19"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="22"/>
       <c r="W37" s="17"/>
       <c r="X37" s="17"/>
       <c r="Y37" s="17"/>
@@ -12510,13 +12518,13 @@
       <c r="O38" s="11"/>
       <c r="P38" s="20"/>
       <c r="Q38" s="21"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="19" t="s">
-        <v>59</v>
+      <c r="R38" s="19" t="s">
+        <v>72</v>
       </c>
-      <c r="T38" s="17"/>
-      <c r="U38" s="19"/>
-      <c r="V38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="19"/>
+      <c r="U38" s="22"/>
+      <c r="V38" s="22"/>
       <c r="W38" s="17"/>
       <c r="X38" s="17"/>
       <c r="Y38" s="17"/>
@@ -12773,8 +12781,8 @@
       <c r="P39" s="20"/>
       <c r="Q39" s="21"/>
       <c r="R39" s="17"/>
-      <c r="S39" s="17" t="s">
-        <v>57</v>
+      <c r="S39" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="T39" s="17"/>
       <c r="U39" s="19"/>
@@ -13033,10 +13041,10 @@
       <c r="N40" s="10"/>
       <c r="O40" s="11"/>
       <c r="P40" s="20"/>
-      <c r="Q40" s="19"/>
+      <c r="Q40" s="21"/>
       <c r="R40" s="17"/>
-      <c r="S40" s="17" t="s">
-        <v>53</v>
+      <c r="S40" s="19" t="s">
+        <v>76</v>
       </c>
       <c r="T40" s="17"/>
       <c r="U40" s="19"/>
@@ -13279,9 +13287,7 @@
       <c r="IX40" s="1"/>
     </row>
     <row r="41" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -13296,11 +13302,11 @@
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
       <c r="O41" s="11"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="17"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="21"/>
       <c r="R41" s="17"/>
-      <c r="S41" s="19" t="s">
-        <v>58</v>
+      <c r="S41" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="T41" s="17"/>
       <c r="U41" s="19"/>
@@ -13558,15 +13564,15 @@
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
       <c r="O42" s="11"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="17" t="s">
-        <v>60</v>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17" t="s">
+        <v>45</v>
       </c>
-      <c r="S42" s="17"/>
       <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
+      <c r="U42" s="19"/>
+      <c r="V42" s="19"/>
       <c r="W42" s="17"/>
       <c r="X42" s="17"/>
       <c r="Y42" s="17"/>
@@ -13805,7 +13811,9 @@
       <c r="IX42" s="1"/>
     </row>
     <row r="43" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
+      <c r="A43" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="B43" s="9"/>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -13824,13 +13832,13 @@
       <c r="Q43" s="17"/>
       <c r="R43" s="17"/>
       <c r="S43" s="19" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="T43" s="17"/>
-      <c r="U43" s="17"/>
-      <c r="V43" s="17"/>
+      <c r="U43" s="19"/>
+      <c r="V43" s="19"/>
       <c r="W43" s="17"/>
-      <c r="X43" s="19"/>
+      <c r="X43" s="17"/>
       <c r="Y43" s="17"/>
       <c r="Z43" s="17"/>
       <c r="AA43" s="17"/>
@@ -14083,11 +14091,11 @@
       <c r="N44" s="10"/>
       <c r="O44" s="11"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="19" t="s">
-        <v>62</v>
+      <c r="Q44" s="23"/>
+      <c r="R44" s="17" t="s">
+        <v>73</v>
       </c>
+      <c r="S44" s="17"/>
       <c r="T44" s="17"/>
       <c r="U44" s="17"/>
       <c r="V44" s="17"/>
@@ -14330,6 +14338,12 @@
     </row>
     <row r="45" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -14341,14 +14355,14 @@
       <c r="P45" s="16"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
-      <c r="S45" s="17" t="s">
-        <v>53</v>
+      <c r="S45" s="19" t="s">
+        <v>77</v>
       </c>
       <c r="T45" s="17"/>
       <c r="U45" s="17"/>
       <c r="V45" s="17"/>
       <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
+      <c r="X45" s="19"/>
       <c r="Y45" s="17"/>
       <c r="Z45" s="17"/>
       <c r="AA45" s="17"/>
@@ -14372,7 +14386,7 @@
       <c r="AS45" s="18"/>
       <c r="AT45" s="8"/>
       <c r="AU45" s="10"/>
-      <c r="AV45" s="9"/>
+      <c r="AV45" s="10"/>
       <c r="AW45" s="10"/>
       <c r="AX45" s="10"/>
       <c r="AY45" s="10"/>
@@ -14585,10 +14599,8 @@
       <c r="IX45" s="1"/>
     </row>
     <row r="46" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" s="10"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="9"/>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
@@ -14602,11 +14614,11 @@
       <c r="M46" s="10"/>
       <c r="N46" s="10"/>
       <c r="O46" s="11"/>
-      <c r="P46" s="55"/>
+      <c r="P46" s="16"/>
       <c r="Q46" s="17"/>
       <c r="R46" s="17"/>
-      <c r="S46" s="17" t="s">
-        <v>63</v>
+      <c r="S46" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="T46" s="17"/>
       <c r="U46" s="17"/>
@@ -14858,12 +14870,12 @@
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
       <c r="O47" s="11"/>
-      <c r="P47" s="51" t="s">
-        <v>82</v>
-      </c>
+      <c r="P47" s="16"/>
       <c r="Q47" s="17"/>
       <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
+      <c r="S47" s="17" t="s">
+        <v>45</v>
+      </c>
       <c r="T47" s="17"/>
       <c r="U47" s="17"/>
       <c r="V47" s="17"/>
@@ -15105,7 +15117,15 @@
       <c r="IX47" s="1"/>
     </row>
     <row r="48" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
+      <c r="A48" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -15114,12 +15134,12 @@
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
       <c r="O48" s="11"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="17" t="s">
-        <v>64</v>
+      <c r="P48" s="34"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17" t="s">
+        <v>84</v>
       </c>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
       <c r="T48" s="17"/>
       <c r="U48" s="17"/>
       <c r="V48" s="17"/>
@@ -15148,7 +15168,7 @@
       <c r="AS48" s="18"/>
       <c r="AT48" s="8"/>
       <c r="AU48" s="10"/>
-      <c r="AV48" s="9"/>
+      <c r="AV48" s="10"/>
       <c r="AW48" s="10"/>
       <c r="AX48" s="10"/>
       <c r="AY48" s="10"/>
@@ -15370,10 +15390,10 @@
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
       <c r="O49" s="11"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="17" t="s">
-        <v>65</v>
+      <c r="P49" s="33" t="s">
+        <v>61</v>
       </c>
+      <c r="Q49" s="17"/>
       <c r="R49" s="17"/>
       <c r="S49" s="17"/>
       <c r="T49" s="17"/>
@@ -15627,7 +15647,9 @@
       <c r="N50" s="10"/>
       <c r="O50" s="11"/>
       <c r="P50" s="16"/>
-      <c r="Q50" s="17"/>
+      <c r="Q50" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="R50" s="17"/>
       <c r="S50" s="17"/>
       <c r="T50" s="17"/>
@@ -15871,67 +15893,63 @@
       <c r="IX50" s="1"/>
     </row>
     <row r="51" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="24"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="25"/>
-      <c r="K51" s="25"/>
-      <c r="L51" s="25"/>
-      <c r="M51" s="25"/>
-      <c r="N51" s="25"/>
-      <c r="O51" s="26"/>
-      <c r="P51" s="30"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="27"/>
-      <c r="S51" s="27"/>
-      <c r="T51" s="27"/>
-      <c r="U51" s="27"/>
-      <c r="V51" s="27"/>
-      <c r="W51" s="27"/>
-      <c r="X51" s="27"/>
-      <c r="Y51" s="27"/>
-      <c r="Z51" s="27"/>
-      <c r="AA51" s="27"/>
-      <c r="AB51" s="27"/>
-      <c r="AC51" s="27"/>
-      <c r="AD51" s="27"/>
-      <c r="AE51" s="27"/>
-      <c r="AF51" s="27"/>
-      <c r="AG51" s="27"/>
-      <c r="AH51" s="27"/>
-      <c r="AI51" s="27"/>
-      <c r="AJ51" s="27"/>
-      <c r="AK51" s="27"/>
-      <c r="AL51" s="27"/>
-      <c r="AM51" s="27"/>
-      <c r="AN51" s="27"/>
-      <c r="AO51" s="27"/>
-      <c r="AP51" s="27"/>
-      <c r="AQ51" s="27"/>
-      <c r="AR51" s="27"/>
-      <c r="AS51" s="28"/>
-      <c r="AT51" s="24"/>
-      <c r="AU51" s="25"/>
-      <c r="AV51" s="31"/>
-      <c r="AW51" s="25"/>
-      <c r="AX51" s="25"/>
-      <c r="AY51" s="25"/>
-      <c r="AZ51" s="25"/>
-      <c r="BA51" s="25"/>
-      <c r="BB51" s="25"/>
-      <c r="BC51" s="25"/>
-      <c r="BD51" s="25"/>
-      <c r="BE51" s="25"/>
-      <c r="BF51" s="25"/>
-      <c r="BG51" s="25"/>
-      <c r="BH51" s="25"/>
-      <c r="BI51" s="26"/>
+      <c r="A51" s="8"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="17"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="17"/>
+      <c r="Z51" s="17"/>
+      <c r="AA51" s="17"/>
+      <c r="AB51" s="17"/>
+      <c r="AC51" s="17"/>
+      <c r="AD51" s="17"/>
+      <c r="AE51" s="17"/>
+      <c r="AF51" s="17"/>
+      <c r="AG51" s="17"/>
+      <c r="AH51" s="17"/>
+      <c r="AI51" s="17"/>
+      <c r="AJ51" s="17"/>
+      <c r="AK51" s="17"/>
+      <c r="AL51" s="17"/>
+      <c r="AM51" s="17"/>
+      <c r="AN51" s="17"/>
+      <c r="AO51" s="17"/>
+      <c r="AP51" s="17"/>
+      <c r="AQ51" s="17"/>
+      <c r="AR51" s="17"/>
+      <c r="AS51" s="18"/>
+      <c r="AT51" s="8"/>
+      <c r="AU51" s="10"/>
+      <c r="AV51" s="9"/>
+      <c r="AW51" s="10"/>
+      <c r="AX51" s="10"/>
+      <c r="AY51" s="10"/>
+      <c r="AZ51" s="10"/>
+      <c r="BA51" s="10"/>
+      <c r="BB51" s="10"/>
+      <c r="BC51" s="10"/>
+      <c r="BD51" s="10"/>
+      <c r="BE51" s="10"/>
+      <c r="BF51" s="10"/>
+      <c r="BG51" s="10"/>
+      <c r="BH51" s="10"/>
+      <c r="BI51" s="11"/>
       <c r="BJ51" s="1"/>
       <c r="BK51" s="1"/>
       <c r="BL51" s="1"/>
@@ -16131,67 +16149,61 @@
       <c r="IX51" s="1"/>
     </row>
     <row r="52" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="13"/>
-      <c r="Q52" s="13"/>
-      <c r="R52" s="13"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="13"/>
-      <c r="U52" s="13"/>
-      <c r="V52" s="13"/>
-      <c r="W52" s="13"/>
-      <c r="X52" s="13"/>
-      <c r="Y52" s="13"/>
-      <c r="Z52" s="13"/>
-      <c r="AA52" s="13"/>
-      <c r="AB52" s="13"/>
-      <c r="AC52" s="13"/>
-      <c r="AD52" s="13"/>
-      <c r="AE52" s="13"/>
-      <c r="AF52" s="13"/>
-      <c r="AG52" s="13"/>
-      <c r="AH52" s="13"/>
-      <c r="AI52" s="13"/>
-      <c r="AJ52" s="13"/>
-      <c r="AK52" s="13"/>
-      <c r="AL52" s="13"/>
-      <c r="AM52" s="13"/>
-      <c r="AN52" s="13"/>
-      <c r="AO52" s="13"/>
-      <c r="AP52" s="13"/>
-      <c r="AQ52" s="13"/>
-      <c r="AR52" s="13"/>
-      <c r="AS52" s="13"/>
-      <c r="AT52" s="13"/>
-      <c r="AU52" s="13"/>
-      <c r="AV52" s="13"/>
-      <c r="AW52" s="13"/>
-      <c r="AX52" s="13"/>
-      <c r="AY52" s="13"/>
-      <c r="AZ52" s="13"/>
-      <c r="BA52" s="13"/>
-      <c r="BB52" s="13"/>
-      <c r="BC52" s="13"/>
-      <c r="BD52" s="13"/>
-      <c r="BE52" s="13"/>
-      <c r="BF52" s="13"/>
-      <c r="BG52" s="13"/>
-      <c r="BH52" s="13"/>
-      <c r="BI52" s="13"/>
+      <c r="A52" s="8"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
+      <c r="Z52" s="17"/>
+      <c r="AA52" s="17"/>
+      <c r="AB52" s="17"/>
+      <c r="AC52" s="17"/>
+      <c r="AD52" s="17"/>
+      <c r="AE52" s="17"/>
+      <c r="AF52" s="17"/>
+      <c r="AG52" s="17"/>
+      <c r="AH52" s="17"/>
+      <c r="AI52" s="17"/>
+      <c r="AJ52" s="17"/>
+      <c r="AK52" s="17"/>
+      <c r="AL52" s="17"/>
+      <c r="AM52" s="17"/>
+      <c r="AN52" s="17"/>
+      <c r="AO52" s="17"/>
+      <c r="AP52" s="17"/>
+      <c r="AQ52" s="17"/>
+      <c r="AR52" s="17"/>
+      <c r="AS52" s="18"/>
+      <c r="AT52" s="8"/>
+      <c r="AU52" s="10"/>
+      <c r="AV52" s="9"/>
+      <c r="AW52" s="10"/>
+      <c r="AX52" s="10"/>
+      <c r="AY52" s="10"/>
+      <c r="AZ52" s="10"/>
+      <c r="BA52" s="10"/>
+      <c r="BB52" s="10"/>
+      <c r="BC52" s="10"/>
+      <c r="BD52" s="10"/>
+      <c r="BE52" s="10"/>
+      <c r="BF52" s="10"/>
+      <c r="BG52" s="10"/>
+      <c r="BH52" s="10"/>
+      <c r="BI52" s="11"/>
       <c r="BJ52" s="1"/>
       <c r="BK52" s="1"/>
       <c r="BL52" s="1"/>
@@ -16390,25 +16402,535 @@
       <c r="IW52" s="1"/>
       <c r="IX52" s="1"/>
     </row>
+    <row r="53" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="24"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="25"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="27"/>
+      <c r="R53" s="27"/>
+      <c r="S53" s="27"/>
+      <c r="T53" s="27"/>
+      <c r="U53" s="27"/>
+      <c r="V53" s="27"/>
+      <c r="W53" s="27"/>
+      <c r="X53" s="27"/>
+      <c r="Y53" s="27"/>
+      <c r="Z53" s="27"/>
+      <c r="AA53" s="27"/>
+      <c r="AB53" s="27"/>
+      <c r="AC53" s="27"/>
+      <c r="AD53" s="27"/>
+      <c r="AE53" s="27"/>
+      <c r="AF53" s="27"/>
+      <c r="AG53" s="27"/>
+      <c r="AH53" s="27"/>
+      <c r="AI53" s="27"/>
+      <c r="AJ53" s="27"/>
+      <c r="AK53" s="27"/>
+      <c r="AL53" s="27"/>
+      <c r="AM53" s="27"/>
+      <c r="AN53" s="27"/>
+      <c r="AO53" s="27"/>
+      <c r="AP53" s="27"/>
+      <c r="AQ53" s="27"/>
+      <c r="AR53" s="27"/>
+      <c r="AS53" s="28"/>
+      <c r="AT53" s="24"/>
+      <c r="AU53" s="25"/>
+      <c r="AV53" s="31"/>
+      <c r="AW53" s="25"/>
+      <c r="AX53" s="25"/>
+      <c r="AY53" s="25"/>
+      <c r="AZ53" s="25"/>
+      <c r="BA53" s="25"/>
+      <c r="BB53" s="25"/>
+      <c r="BC53" s="25"/>
+      <c r="BD53" s="25"/>
+      <c r="BE53" s="25"/>
+      <c r="BF53" s="25"/>
+      <c r="BG53" s="25"/>
+      <c r="BH53" s="25"/>
+      <c r="BI53" s="26"/>
+      <c r="BJ53" s="1"/>
+      <c r="BK53" s="1"/>
+      <c r="BL53" s="1"/>
+      <c r="BM53" s="1"/>
+      <c r="BN53" s="1"/>
+      <c r="BO53" s="1"/>
+      <c r="BP53" s="1"/>
+      <c r="BQ53" s="1"/>
+      <c r="BR53" s="1"/>
+      <c r="BS53" s="1"/>
+      <c r="BT53" s="1"/>
+      <c r="BU53" s="1"/>
+      <c r="BV53" s="1"/>
+      <c r="BW53" s="1"/>
+      <c r="BX53" s="1"/>
+      <c r="BY53" s="1"/>
+      <c r="BZ53" s="1"/>
+      <c r="CA53" s="1"/>
+      <c r="CB53" s="1"/>
+      <c r="CC53" s="1"/>
+      <c r="CD53" s="1"/>
+      <c r="CE53" s="1"/>
+      <c r="CF53" s="1"/>
+      <c r="CG53" s="1"/>
+      <c r="CH53" s="1"/>
+      <c r="CI53" s="1"/>
+      <c r="CJ53" s="1"/>
+      <c r="CK53" s="1"/>
+      <c r="CL53" s="1"/>
+      <c r="CM53" s="1"/>
+      <c r="CN53" s="1"/>
+      <c r="CO53" s="1"/>
+      <c r="CP53" s="1"/>
+      <c r="CQ53" s="1"/>
+      <c r="CR53" s="1"/>
+      <c r="CS53" s="1"/>
+      <c r="CT53" s="1"/>
+      <c r="CU53" s="1"/>
+      <c r="CV53" s="1"/>
+      <c r="CW53" s="1"/>
+      <c r="CX53" s="1"/>
+      <c r="CY53" s="1"/>
+      <c r="CZ53" s="1"/>
+      <c r="DA53" s="1"/>
+      <c r="DB53" s="1"/>
+      <c r="DC53" s="1"/>
+      <c r="DD53" s="1"/>
+      <c r="DE53" s="1"/>
+      <c r="DF53" s="1"/>
+      <c r="DG53" s="1"/>
+      <c r="DH53" s="1"/>
+      <c r="DI53" s="1"/>
+      <c r="DJ53" s="1"/>
+      <c r="DK53" s="1"/>
+      <c r="DL53" s="1"/>
+      <c r="DM53" s="1"/>
+      <c r="DN53" s="1"/>
+      <c r="DO53" s="1"/>
+      <c r="DP53" s="1"/>
+      <c r="DQ53" s="1"/>
+      <c r="DR53" s="1"/>
+      <c r="DS53" s="1"/>
+      <c r="DT53" s="1"/>
+      <c r="DU53" s="1"/>
+      <c r="DV53" s="1"/>
+      <c r="DW53" s="1"/>
+      <c r="DX53" s="1"/>
+      <c r="DY53" s="1"/>
+      <c r="DZ53" s="1"/>
+      <c r="EA53" s="1"/>
+      <c r="EB53" s="1"/>
+      <c r="EC53" s="1"/>
+      <c r="ED53" s="1"/>
+      <c r="EE53" s="1"/>
+      <c r="EF53" s="1"/>
+      <c r="EG53" s="1"/>
+      <c r="EH53" s="1"/>
+      <c r="EI53" s="1"/>
+      <c r="EJ53" s="1"/>
+      <c r="EK53" s="1"/>
+      <c r="EL53" s="1"/>
+      <c r="EM53" s="1"/>
+      <c r="EN53" s="1"/>
+      <c r="EO53" s="1"/>
+      <c r="EP53" s="1"/>
+      <c r="EQ53" s="1"/>
+      <c r="ER53" s="1"/>
+      <c r="ES53" s="1"/>
+      <c r="ET53" s="1"/>
+      <c r="EU53" s="1"/>
+      <c r="EV53" s="1"/>
+      <c r="EW53" s="1"/>
+      <c r="EX53" s="1"/>
+      <c r="EY53" s="1"/>
+      <c r="EZ53" s="1"/>
+      <c r="FA53" s="1"/>
+      <c r="FB53" s="1"/>
+      <c r="FC53" s="1"/>
+      <c r="FD53" s="1"/>
+      <c r="FE53" s="1"/>
+      <c r="FF53" s="1"/>
+      <c r="FG53" s="1"/>
+      <c r="FH53" s="1"/>
+      <c r="FI53" s="1"/>
+      <c r="FJ53" s="1"/>
+      <c r="FK53" s="1"/>
+      <c r="FL53" s="1"/>
+      <c r="FM53" s="1"/>
+      <c r="FN53" s="1"/>
+      <c r="FO53" s="1"/>
+      <c r="FP53" s="1"/>
+      <c r="FQ53" s="1"/>
+      <c r="FR53" s="1"/>
+      <c r="FS53" s="1"/>
+      <c r="FT53" s="1"/>
+      <c r="FU53" s="1"/>
+      <c r="FV53" s="1"/>
+      <c r="FW53" s="1"/>
+      <c r="FX53" s="1"/>
+      <c r="FY53" s="1"/>
+      <c r="FZ53" s="1"/>
+      <c r="GA53" s="1"/>
+      <c r="GB53" s="1"/>
+      <c r="GC53" s="1"/>
+      <c r="GD53" s="1"/>
+      <c r="GE53" s="1"/>
+      <c r="GF53" s="1"/>
+      <c r="GG53" s="1"/>
+      <c r="GH53" s="1"/>
+      <c r="GI53" s="1"/>
+      <c r="GJ53" s="1"/>
+      <c r="GK53" s="1"/>
+      <c r="GL53" s="1"/>
+      <c r="GM53" s="1"/>
+      <c r="GN53" s="1"/>
+      <c r="GO53" s="1"/>
+      <c r="GP53" s="1"/>
+      <c r="GQ53" s="1"/>
+      <c r="GR53" s="1"/>
+      <c r="GS53" s="1"/>
+      <c r="GT53" s="1"/>
+      <c r="GU53" s="1"/>
+      <c r="GV53" s="1"/>
+      <c r="GW53" s="1"/>
+      <c r="GX53" s="1"/>
+      <c r="GY53" s="1"/>
+      <c r="GZ53" s="1"/>
+      <c r="HA53" s="1"/>
+      <c r="HB53" s="1"/>
+      <c r="HC53" s="1"/>
+      <c r="HD53" s="1"/>
+      <c r="HE53" s="1"/>
+      <c r="HF53" s="1"/>
+      <c r="HG53" s="1"/>
+      <c r="HH53" s="1"/>
+      <c r="HI53" s="1"/>
+      <c r="HJ53" s="1"/>
+      <c r="HK53" s="1"/>
+      <c r="HL53" s="1"/>
+      <c r="HM53" s="1"/>
+      <c r="HN53" s="1"/>
+      <c r="HO53" s="1"/>
+      <c r="HP53" s="1"/>
+      <c r="HQ53" s="1"/>
+      <c r="HR53" s="1"/>
+      <c r="HS53" s="1"/>
+      <c r="HT53" s="1"/>
+      <c r="HU53" s="1"/>
+      <c r="HV53" s="1"/>
+      <c r="HW53" s="1"/>
+      <c r="HX53" s="1"/>
+      <c r="HY53" s="1"/>
+      <c r="HZ53" s="1"/>
+      <c r="IA53" s="1"/>
+      <c r="IB53" s="1"/>
+      <c r="IC53" s="1"/>
+      <c r="ID53" s="1"/>
+      <c r="IE53" s="1"/>
+      <c r="IF53" s="1"/>
+      <c r="IG53" s="1"/>
+      <c r="IH53" s="1"/>
+      <c r="II53" s="1"/>
+      <c r="IJ53" s="1"/>
+      <c r="IK53" s="1"/>
+      <c r="IL53" s="1"/>
+      <c r="IM53" s="1"/>
+      <c r="IN53" s="1"/>
+      <c r="IO53" s="1"/>
+      <c r="IP53" s="1"/>
+      <c r="IQ53" s="1"/>
+      <c r="IR53" s="1"/>
+      <c r="IS53" s="1"/>
+      <c r="IT53" s="1"/>
+      <c r="IU53" s="1"/>
+      <c r="IV53" s="1"/>
+      <c r="IW53" s="1"/>
+      <c r="IX53" s="1"/>
+    </row>
+    <row r="54" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="13"/>
+      <c r="U54" s="13"/>
+      <c r="V54" s="13"/>
+      <c r="W54" s="13"/>
+      <c r="X54" s="13"/>
+      <c r="Y54" s="13"/>
+      <c r="Z54" s="13"/>
+      <c r="AA54" s="13"/>
+      <c r="AB54" s="13"/>
+      <c r="AC54" s="13"/>
+      <c r="AD54" s="13"/>
+      <c r="AE54" s="13"/>
+      <c r="AF54" s="13"/>
+      <c r="AG54" s="13"/>
+      <c r="AH54" s="13"/>
+      <c r="AI54" s="13"/>
+      <c r="AJ54" s="13"/>
+      <c r="AK54" s="13"/>
+      <c r="AL54" s="13"/>
+      <c r="AM54" s="13"/>
+      <c r="AN54" s="13"/>
+      <c r="AO54" s="13"/>
+      <c r="AP54" s="13"/>
+      <c r="AQ54" s="13"/>
+      <c r="AR54" s="13"/>
+      <c r="AS54" s="13"/>
+      <c r="AT54" s="13"/>
+      <c r="AU54" s="13"/>
+      <c r="AV54" s="13"/>
+      <c r="AW54" s="13"/>
+      <c r="AX54" s="13"/>
+      <c r="AY54" s="13"/>
+      <c r="AZ54" s="13"/>
+      <c r="BA54" s="13"/>
+      <c r="BB54" s="13"/>
+      <c r="BC54" s="13"/>
+      <c r="BD54" s="13"/>
+      <c r="BE54" s="13"/>
+      <c r="BF54" s="13"/>
+      <c r="BG54" s="13"/>
+      <c r="BH54" s="13"/>
+      <c r="BI54" s="13"/>
+      <c r="BJ54" s="1"/>
+      <c r="BK54" s="1"/>
+      <c r="BL54" s="1"/>
+      <c r="BM54" s="1"/>
+      <c r="BN54" s="1"/>
+      <c r="BO54" s="1"/>
+      <c r="BP54" s="1"/>
+      <c r="BQ54" s="1"/>
+      <c r="BR54" s="1"/>
+      <c r="BS54" s="1"/>
+      <c r="BT54" s="1"/>
+      <c r="BU54" s="1"/>
+      <c r="BV54" s="1"/>
+      <c r="BW54" s="1"/>
+      <c r="BX54" s="1"/>
+      <c r="BY54" s="1"/>
+      <c r="BZ54" s="1"/>
+      <c r="CA54" s="1"/>
+      <c r="CB54" s="1"/>
+      <c r="CC54" s="1"/>
+      <c r="CD54" s="1"/>
+      <c r="CE54" s="1"/>
+      <c r="CF54" s="1"/>
+      <c r="CG54" s="1"/>
+      <c r="CH54" s="1"/>
+      <c r="CI54" s="1"/>
+      <c r="CJ54" s="1"/>
+      <c r="CK54" s="1"/>
+      <c r="CL54" s="1"/>
+      <c r="CM54" s="1"/>
+      <c r="CN54" s="1"/>
+      <c r="CO54" s="1"/>
+      <c r="CP54" s="1"/>
+      <c r="CQ54" s="1"/>
+      <c r="CR54" s="1"/>
+      <c r="CS54" s="1"/>
+      <c r="CT54" s="1"/>
+      <c r="CU54" s="1"/>
+      <c r="CV54" s="1"/>
+      <c r="CW54" s="1"/>
+      <c r="CX54" s="1"/>
+      <c r="CY54" s="1"/>
+      <c r="CZ54" s="1"/>
+      <c r="DA54" s="1"/>
+      <c r="DB54" s="1"/>
+      <c r="DC54" s="1"/>
+      <c r="DD54" s="1"/>
+      <c r="DE54" s="1"/>
+      <c r="DF54" s="1"/>
+      <c r="DG54" s="1"/>
+      <c r="DH54" s="1"/>
+      <c r="DI54" s="1"/>
+      <c r="DJ54" s="1"/>
+      <c r="DK54" s="1"/>
+      <c r="DL54" s="1"/>
+      <c r="DM54" s="1"/>
+      <c r="DN54" s="1"/>
+      <c r="DO54" s="1"/>
+      <c r="DP54" s="1"/>
+      <c r="DQ54" s="1"/>
+      <c r="DR54" s="1"/>
+      <c r="DS54" s="1"/>
+      <c r="DT54" s="1"/>
+      <c r="DU54" s="1"/>
+      <c r="DV54" s="1"/>
+      <c r="DW54" s="1"/>
+      <c r="DX54" s="1"/>
+      <c r="DY54" s="1"/>
+      <c r="DZ54" s="1"/>
+      <c r="EA54" s="1"/>
+      <c r="EB54" s="1"/>
+      <c r="EC54" s="1"/>
+      <c r="ED54" s="1"/>
+      <c r="EE54" s="1"/>
+      <c r="EF54" s="1"/>
+      <c r="EG54" s="1"/>
+      <c r="EH54" s="1"/>
+      <c r="EI54" s="1"/>
+      <c r="EJ54" s="1"/>
+      <c r="EK54" s="1"/>
+      <c r="EL54" s="1"/>
+      <c r="EM54" s="1"/>
+      <c r="EN54" s="1"/>
+      <c r="EO54" s="1"/>
+      <c r="EP54" s="1"/>
+      <c r="EQ54" s="1"/>
+      <c r="ER54" s="1"/>
+      <c r="ES54" s="1"/>
+      <c r="ET54" s="1"/>
+      <c r="EU54" s="1"/>
+      <c r="EV54" s="1"/>
+      <c r="EW54" s="1"/>
+      <c r="EX54" s="1"/>
+      <c r="EY54" s="1"/>
+      <c r="EZ54" s="1"/>
+      <c r="FA54" s="1"/>
+      <c r="FB54" s="1"/>
+      <c r="FC54" s="1"/>
+      <c r="FD54" s="1"/>
+      <c r="FE54" s="1"/>
+      <c r="FF54" s="1"/>
+      <c r="FG54" s="1"/>
+      <c r="FH54" s="1"/>
+      <c r="FI54" s="1"/>
+      <c r="FJ54" s="1"/>
+      <c r="FK54" s="1"/>
+      <c r="FL54" s="1"/>
+      <c r="FM54" s="1"/>
+      <c r="FN54" s="1"/>
+      <c r="FO54" s="1"/>
+      <c r="FP54" s="1"/>
+      <c r="FQ54" s="1"/>
+      <c r="FR54" s="1"/>
+      <c r="FS54" s="1"/>
+      <c r="FT54" s="1"/>
+      <c r="FU54" s="1"/>
+      <c r="FV54" s="1"/>
+      <c r="FW54" s="1"/>
+      <c r="FX54" s="1"/>
+      <c r="FY54" s="1"/>
+      <c r="FZ54" s="1"/>
+      <c r="GA54" s="1"/>
+      <c r="GB54" s="1"/>
+      <c r="GC54" s="1"/>
+      <c r="GD54" s="1"/>
+      <c r="GE54" s="1"/>
+      <c r="GF54" s="1"/>
+      <c r="GG54" s="1"/>
+      <c r="GH54" s="1"/>
+      <c r="GI54" s="1"/>
+      <c r="GJ54" s="1"/>
+      <c r="GK54" s="1"/>
+      <c r="GL54" s="1"/>
+      <c r="GM54" s="1"/>
+      <c r="GN54" s="1"/>
+      <c r="GO54" s="1"/>
+      <c r="GP54" s="1"/>
+      <c r="GQ54" s="1"/>
+      <c r="GR54" s="1"/>
+      <c r="GS54" s="1"/>
+      <c r="GT54" s="1"/>
+      <c r="GU54" s="1"/>
+      <c r="GV54" s="1"/>
+      <c r="GW54" s="1"/>
+      <c r="GX54" s="1"/>
+      <c r="GY54" s="1"/>
+      <c r="GZ54" s="1"/>
+      <c r="HA54" s="1"/>
+      <c r="HB54" s="1"/>
+      <c r="HC54" s="1"/>
+      <c r="HD54" s="1"/>
+      <c r="HE54" s="1"/>
+      <c r="HF54" s="1"/>
+      <c r="HG54" s="1"/>
+      <c r="HH54" s="1"/>
+      <c r="HI54" s="1"/>
+      <c r="HJ54" s="1"/>
+      <c r="HK54" s="1"/>
+      <c r="HL54" s="1"/>
+      <c r="HM54" s="1"/>
+      <c r="HN54" s="1"/>
+      <c r="HO54" s="1"/>
+      <c r="HP54" s="1"/>
+      <c r="HQ54" s="1"/>
+      <c r="HR54" s="1"/>
+      <c r="HS54" s="1"/>
+      <c r="HT54" s="1"/>
+      <c r="HU54" s="1"/>
+      <c r="HV54" s="1"/>
+      <c r="HW54" s="1"/>
+      <c r="HX54" s="1"/>
+      <c r="HY54" s="1"/>
+      <c r="HZ54" s="1"/>
+      <c r="IA54" s="1"/>
+      <c r="IB54" s="1"/>
+      <c r="IC54" s="1"/>
+      <c r="ID54" s="1"/>
+      <c r="IE54" s="1"/>
+      <c r="IF54" s="1"/>
+      <c r="IG54" s="1"/>
+      <c r="IH54" s="1"/>
+      <c r="II54" s="1"/>
+      <c r="IJ54" s="1"/>
+      <c r="IK54" s="1"/>
+      <c r="IL54" s="1"/>
+      <c r="IM54" s="1"/>
+      <c r="IN54" s="1"/>
+      <c r="IO54" s="1"/>
+      <c r="IP54" s="1"/>
+      <c r="IQ54" s="1"/>
+      <c r="IR54" s="1"/>
+      <c r="IS54" s="1"/>
+      <c r="IT54" s="1"/>
+      <c r="IU54" s="1"/>
+      <c r="IV54" s="1"/>
+      <c r="IW54" s="1"/>
+      <c r="IX54" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="P12:AS12"/>
-    <mergeCell ref="AT12:BI12"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:BI10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:BI5"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="M2:Q2"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="R1:AA1"/>
     <mergeCell ref="AB1:AD1"/>
@@ -16423,13 +16945,23 @@
     <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="AT2:AZ2"/>
     <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:BI5"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="P12:AS12"/>
+    <mergeCell ref="AT12:BI12"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:BI10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
@@ -16454,6 +16986,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -16585,12 +17123,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
   <ds:schemaRefs>
@@ -16600,6 +17132,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7560E91F-1ABF-4BEF-A078-A8FA5AD9AA18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16615,13 +17156,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/03_内部設計/022-クラス仕様書/util/PagingUtilのクラス仕様書.xlsx
+++ b/03_内部設計/022-クラス仕様書/util/PagingUtilのクラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7D727A-D797-4C12-AFBA-4B810D0D6B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09B1F02-F68B-4ADC-BBF5-ECFC1903474A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（paging）'!$A$1:$BI$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（paging）'!$A$1:$BI$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -242,45 +242,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.1.1) 最大10件分のデータをf、or文でsplitedListに格納する</t>
-    <rPh sb="24" eb="25">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カクノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.4.2.1) 現在表示しているページ数をJSPから取得する。</t>
-    <rPh sb="9" eb="13">
-      <t>ゲンザイヒョウジ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>splitedListに最初に格納する検索結果の要素番号を代入する。</t>
-  </si>
-  <si>
-    <t>3.4.3.1) 現在表示しているページ数をJSPから取得する。</t>
-    <rPh sb="9" eb="13">
-      <t>ゲンザイヒョウジ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>4.2) "splitedList"でsplitedList</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -464,7 +425,26 @@
     <t>3.1.1) 取得したデータはString型の変数、requestedに代入する。</t>
   </si>
   <si>
-    <t>3.4) requestedの値からif-else if文で条件分岐処理を行う。</t>
+    <t>4.1) "now"でnow</t>
+  </si>
+  <si>
+    <t>3.2.1) List&lt;ItemsDTO&gt;型のArrayList、splitedListを生成する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.5) for文とstartを用いて、最大10件分のデータをsplitedListに格納する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.3) int型の変数、nowを1で初期化する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.4) int型の変数、startを0で初期化する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.5) requestedの値からif-else if文で条件分岐処理を行う。</t>
     <rPh sb="15" eb="16">
       <t>アタイ</t>
     </rPh>
@@ -480,7 +460,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.1) requestedがnullの場合(初回アクセス時)</t>
+    <t>3.5.1) requestedがnullの場合(初回アクセス時)、何もしない。</t>
     <rPh sb="22" eb="24">
       <t>バアイ</t>
     </rPh>
@@ -490,10 +470,13 @@
     <rPh sb="31" eb="32">
       <t>ジ</t>
     </rPh>
+    <rPh sb="34" eb="35">
+      <t>ナニ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.2) requestedの値が"次へ"の場合</t>
+    <t>3.5.2) requestedの値が"次へ"の場合</t>
     <rPh sb="17" eb="18">
       <t>アタイ</t>
     </rPh>
@@ -506,93 +489,94 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.3) requestedの値が"前へ"の場合</t>
+    <t>3.5.3) requestedの値が"前へ"の場合</t>
     <rPh sb="20" eb="21">
       <t>マエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.4) requestedの値が数値の場合</t>
-    <rPh sb="17" eb="18">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>バアイ</t>
-    </rPh>
+    <t>10 * (now - 1)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.3) int型の変数、nowを１で初期化する。</t>
-  </si>
-  <si>
-    <t>3.4.2.2) (取得したページ数) + 1をnowに代入する。</t>
-  </si>
-  <si>
-    <t>3.4.3.2) (取得したページ数) - 1をnowに代入する。</t>
-  </si>
-  <si>
-    <t>3.4.4.1) 現在表示しているページ数をJSPから取得し、nowに代入する。</t>
+    <t>3.5.2.1) 現在表示しているページ数をセッションオブジェクトから取得する。</t>
     <rPh sb="9" eb="13">
       <t>ゲンザイヒョウジ</t>
     </rPh>
     <rPh sb="20" eb="21">
       <t>スウ</t>
     </rPh>
-    <rPh sb="27" eb="29">
+    <rPh sb="35" eb="37">
       <t>シュトク</t>
     </rPh>
-    <rPh sb="35" eb="37">
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.5.2.2) (取得したページ数) + 1をnowに代入する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.5.2.3) 以下の数式をstartに代入する。</t>
+    <rPh sb="9" eb="11">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スウシキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
       <t>ダイニュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4.1) "now"でnow</t>
-  </si>
-  <si>
-    <t>3.4.2.3) int型の変数、startを宣言し、</t>
-    <rPh sb="12" eb="13">
-      <t>ガタ</t>
+    <t>3.5.3.1) 現在表示しているページ数をセッションオブジェクトから取得する。</t>
+    <rPh sb="9" eb="13">
+      <t>ゲンザイヒョウジ</t>
     </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヘンスウ</t>
+    <rPh sb="20" eb="21">
+      <t>スウ</t>
     </rPh>
-    <rPh sb="23" eb="25">
-      <t>センゲン</t>
+    <rPh sb="35" eb="37">
+      <t>シュトク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.2.4) for文とstartを用いて、最大10件分のデータをsplitedListに格納する。</t>
+    <t>3.5.3.2) (取得したページ数) - 1をnowに代入する。</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.3.3) int型の変数、startを宣言し、</t>
-    <rPh sb="12" eb="13">
-      <t>ガタ</t>
+    <t>3.5.4) requestedの値が3.5.1-3.5.3 以外の場合</t>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
     </rPh>
-    <rPh sb="14" eb="16">
-      <t>ヘンスウ</t>
+    <rPh sb="31" eb="33">
+      <t>イガイ</t>
     </rPh>
-    <rPh sb="23" eb="25">
-      <t>センゲン</t>
+    <rPh sb="34" eb="36">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.3.4) for文とstartを用いて、最大10件分のデータをsplitedListに格納する。</t>
+    <t>3.5.4.1) 現在表示しているページ数をセッションオブジェクトから取得し、nowに代入する。</t>
+    <rPh sb="9" eb="13">
+      <t>ゲンザイヒョウジ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ダイニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3.4.4.2) int型の変数、startを宣言し、</t>
-  </si>
-  <si>
-    <t>3.4.4.3) for文とstartを用いて、最大10件分のデータをsplitedListに格納する。</t>
-  </si>
-  <si>
-    <t>3.2.1) List&lt;ItemsDTO&gt;型のArrayList、splitedListを生成する。</t>
+    <t>3.5.4.2) 以下の数式をstartに代入する。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -946,16 +930,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -966,13 +944,13 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -981,14 +959,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -998,15 +991,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1372,71 +1356,71 @@
       <c r="J1" s="42"/>
       <c r="K1" s="42"/>
       <c r="L1" s="42"/>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="43" t="s">
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="44" t="s">
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="43" t="s">
-        <v>49</v>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="36" t="s">
+        <v>45</v>
       </c>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="43"/>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="43"/>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="44" t="s">
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="44"/>
-      <c r="AS1" s="44"/>
-      <c r="AT1" s="43" t="s">
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="43"/>
-      <c r="AV1" s="43"/>
-      <c r="AW1" s="43"/>
-      <c r="AX1" s="43"/>
-      <c r="AY1" s="43"/>
-      <c r="AZ1" s="43"/>
-      <c r="BA1" s="44" t="s">
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
+      <c r="AY1" s="36"/>
+      <c r="AZ1" s="36"/>
+      <c r="BA1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="44"/>
-      <c r="BC1" s="44"/>
-      <c r="BD1" s="45">
+      <c r="BB1" s="35"/>
+      <c r="BC1" s="35"/>
+      <c r="BD1" s="43">
         <v>45555</v>
       </c>
-      <c r="BE1" s="45"/>
-      <c r="BF1" s="45"/>
-      <c r="BG1" s="45"/>
-      <c r="BH1" s="45"/>
-      <c r="BI1" s="45"/>
+      <c r="BE1" s="43"/>
+      <c r="BF1" s="43"/>
+      <c r="BG1" s="43"/>
+      <c r="BH1" s="43"/>
+      <c r="BI1" s="43"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1648,70 +1632,70 @@
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
       <c r="L2" s="42"/>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="44" t="s">
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="43" t="str">
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="36" t="str">
         <f>G5</f>
         <v>PagingUtil</v>
       </c>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="43"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43"/>
-      <c r="AQ2" s="44" t="s">
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="44"/>
-      <c r="AS2" s="44"/>
-      <c r="AT2" s="43" t="s">
-        <v>50</v>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="36" t="s">
+        <v>46</v>
       </c>
-      <c r="AU2" s="43"/>
-      <c r="AV2" s="43"/>
-      <c r="AW2" s="43"/>
-      <c r="AX2" s="43"/>
-      <c r="AY2" s="43"/>
-      <c r="AZ2" s="43"/>
-      <c r="BA2" s="44" t="s">
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="44"/>
-      <c r="BC2" s="44"/>
-      <c r="BD2" s="39">
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="37">
         <v>45566</v>
       </c>
-      <c r="BE2" s="40"/>
-      <c r="BF2" s="40"/>
-      <c r="BG2" s="40"/>
-      <c r="BH2" s="40"/>
-      <c r="BI2" s="41"/>
+      <c r="BE2" s="38"/>
+      <c r="BF2" s="38"/>
+      <c r="BG2" s="38"/>
+      <c r="BH2" s="38"/>
+      <c r="BI2" s="39"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1974,927 +1958,942 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="38" t="s">
-        <v>52</v>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41" t="s">
+        <v>48</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="41"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="41"/>
+      <c r="BG4" s="41"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="41"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="41"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="41"/>
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="41"/>
+      <c r="BG5" s="41"/>
+      <c r="BH5" s="41"/>
+      <c r="BI5" s="41"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="38" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="38"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="36" t="s">
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="41"/>
+      <c r="AD6" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="AE6" s="36"/>
-      <c r="AF6" s="36"/>
-      <c r="AG6" s="36"/>
-      <c r="AH6" s="36"/>
-      <c r="AI6" s="36"/>
-      <c r="AJ6" s="38" t="s">
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="40"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="AK6" s="38"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="38"/>
-      <c r="AN6" s="38"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="38"/>
-      <c r="AQ6" s="38"/>
-      <c r="AR6" s="38"/>
-      <c r="AS6" s="38"/>
-      <c r="AT6" s="38"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="38"/>
-      <c r="AX6" s="38"/>
-      <c r="AY6" s="38"/>
-      <c r="AZ6" s="38"/>
-      <c r="BA6" s="38"/>
-      <c r="BB6" s="38"/>
-      <c r="BC6" s="38"/>
-      <c r="BD6" s="38"/>
-      <c r="BE6" s="38"/>
-      <c r="BF6" s="38"/>
-      <c r="BG6" s="38"/>
-      <c r="BH6" s="38"/>
-      <c r="BI6" s="38"/>
+      <c r="AK6" s="41"/>
+      <c r="AL6" s="41"/>
+      <c r="AM6" s="41"/>
+      <c r="AN6" s="41"/>
+      <c r="AO6" s="41"/>
+      <c r="AP6" s="41"/>
+      <c r="AQ6" s="41"/>
+      <c r="AR6" s="41"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="41"/>
+      <c r="AU6" s="41"/>
+      <c r="AV6" s="41"/>
+      <c r="AW6" s="41"/>
+      <c r="AX6" s="41"/>
+      <c r="AY6" s="41"/>
+      <c r="AZ6" s="41"/>
+      <c r="BA6" s="41"/>
+      <c r="BB6" s="41"/>
+      <c r="BC6" s="41"/>
+      <c r="BD6" s="41"/>
+      <c r="BE6" s="41"/>
+      <c r="BF6" s="41"/>
+      <c r="BG6" s="41"/>
+      <c r="BH6" s="41"/>
+      <c r="BI6" s="41"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36" t="s">
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="36"/>
-      <c r="AD8" s="36"/>
-      <c r="AE8" s="36" t="s">
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="40"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="40"/>
+      <c r="AE8" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="AF8" s="36"/>
-      <c r="AG8" s="36"/>
-      <c r="AH8" s="36"/>
-      <c r="AI8" s="36"/>
-      <c r="AJ8" s="36"/>
-      <c r="AK8" s="36"/>
-      <c r="AL8" s="36"/>
-      <c r="AM8" s="36"/>
-      <c r="AN8" s="36"/>
-      <c r="AO8" s="36" t="s">
+      <c r="AF8" s="40"/>
+      <c r="AG8" s="40"/>
+      <c r="AH8" s="40"/>
+      <c r="AI8" s="40"/>
+      <c r="AJ8" s="40"/>
+      <c r="AK8" s="40"/>
+      <c r="AL8" s="40"/>
+      <c r="AM8" s="40"/>
+      <c r="AN8" s="40"/>
+      <c r="AO8" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="AP8" s="36"/>
-      <c r="AQ8" s="36"/>
-      <c r="AR8" s="36"/>
-      <c r="AS8" s="36"/>
-      <c r="AT8" s="36"/>
-      <c r="AU8" s="36"/>
-      <c r="AV8" s="36"/>
-      <c r="AW8" s="36"/>
-      <c r="AX8" s="36"/>
-      <c r="AY8" s="36"/>
-      <c r="AZ8" s="36"/>
-      <c r="BA8" s="36"/>
-      <c r="BB8" s="36"/>
-      <c r="BC8" s="36"/>
-      <c r="BD8" s="36"/>
-      <c r="BE8" s="36"/>
-      <c r="BF8" s="36"/>
-      <c r="BG8" s="36"/>
-      <c r="BH8" s="36"/>
-      <c r="BI8" s="36"/>
+      <c r="AP8" s="40"/>
+      <c r="AQ8" s="40"/>
+      <c r="AR8" s="40"/>
+      <c r="AS8" s="40"/>
+      <c r="AT8" s="40"/>
+      <c r="AU8" s="40"/>
+      <c r="AV8" s="40"/>
+      <c r="AW8" s="40"/>
+      <c r="AX8" s="40"/>
+      <c r="AY8" s="40"/>
+      <c r="AZ8" s="40"/>
+      <c r="BA8" s="40"/>
+      <c r="BB8" s="40"/>
+      <c r="BC8" s="40"/>
+      <c r="BD8" s="40"/>
+      <c r="BE8" s="40"/>
+      <c r="BF8" s="40"/>
+      <c r="BG8" s="40"/>
+      <c r="BH8" s="40"/>
+      <c r="BI8" s="40"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="37"/>
-      <c r="AF9" s="37"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="37"/>
-      <c r="AI9" s="37"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="37"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="37"/>
-      <c r="AP9" s="37"/>
-      <c r="AQ9" s="37"/>
-      <c r="AR9" s="37"/>
-      <c r="AS9" s="37"/>
-      <c r="AT9" s="37"/>
-      <c r="AU9" s="37"/>
-      <c r="AV9" s="37"/>
-      <c r="AW9" s="37"/>
-      <c r="AX9" s="37"/>
-      <c r="AY9" s="37"/>
-      <c r="AZ9" s="37"/>
-      <c r="BA9" s="37"/>
-      <c r="BB9" s="37"/>
-      <c r="BC9" s="37"/>
-      <c r="BD9" s="37"/>
-      <c r="BE9" s="37"/>
-      <c r="BF9" s="37"/>
-      <c r="BG9" s="37"/>
-      <c r="BH9" s="37"/>
-      <c r="BI9" s="37"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="45"/>
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="45"/>
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45"/>
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45"/>
+      <c r="AI9" s="45"/>
+      <c r="AJ9" s="45"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="45"/>
+      <c r="AM9" s="45"/>
+      <c r="AN9" s="45"/>
+      <c r="AO9" s="45"/>
+      <c r="AP9" s="45"/>
+      <c r="AQ9" s="45"/>
+      <c r="AR9" s="45"/>
+      <c r="AS9" s="45"/>
+      <c r="AT9" s="45"/>
+      <c r="AU9" s="45"/>
+      <c r="AV9" s="45"/>
+      <c r="AW9" s="45"/>
+      <c r="AX9" s="45"/>
+      <c r="AY9" s="45"/>
+      <c r="AZ9" s="45"/>
+      <c r="BA9" s="45"/>
+      <c r="BB9" s="45"/>
+      <c r="BC9" s="45"/>
+      <c r="BD9" s="45"/>
+      <c r="BE9" s="45"/>
+      <c r="BF9" s="45"/>
+      <c r="BG9" s="45"/>
+      <c r="BH9" s="45"/>
+      <c r="BI9" s="45"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="37"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="37"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="37"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37"/>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="37"/>
-      <c r="AM10" s="37"/>
-      <c r="AN10" s="37"/>
-      <c r="AO10" s="37"/>
-      <c r="AP10" s="37"/>
-      <c r="AQ10" s="37"/>
-      <c r="AR10" s="37"/>
-      <c r="AS10" s="37"/>
-      <c r="AT10" s="37"/>
-      <c r="AU10" s="37"/>
-      <c r="AV10" s="37"/>
-      <c r="AW10" s="37"/>
-      <c r="AX10" s="37"/>
-      <c r="AY10" s="37"/>
-      <c r="AZ10" s="37"/>
-      <c r="BA10" s="37"/>
-      <c r="BB10" s="37"/>
-      <c r="BC10" s="37"/>
-      <c r="BD10" s="37"/>
-      <c r="BE10" s="37"/>
-      <c r="BF10" s="37"/>
-      <c r="BG10" s="37"/>
-      <c r="BH10" s="37"/>
-      <c r="BI10" s="37"/>
+      <c r="A10" s="45"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="45"/>
+      <c r="R10" s="45"/>
+      <c r="S10" s="45"/>
+      <c r="T10" s="45"/>
+      <c r="U10" s="45"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="45"/>
+      <c r="X10" s="45"/>
+      <c r="Y10" s="45"/>
+      <c r="Z10" s="45"/>
+      <c r="AA10" s="45"/>
+      <c r="AB10" s="45"/>
+      <c r="AC10" s="45"/>
+      <c r="AD10" s="45"/>
+      <c r="AE10" s="45"/>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="45"/>
+      <c r="AH10" s="45"/>
+      <c r="AI10" s="45"/>
+      <c r="AJ10" s="45"/>
+      <c r="AK10" s="45"/>
+      <c r="AL10" s="45"/>
+      <c r="AM10" s="45"/>
+      <c r="AN10" s="45"/>
+      <c r="AO10" s="45"/>
+      <c r="AP10" s="45"/>
+      <c r="AQ10" s="45"/>
+      <c r="AR10" s="45"/>
+      <c r="AS10" s="45"/>
+      <c r="AT10" s="45"/>
+      <c r="AU10" s="45"/>
+      <c r="AV10" s="45"/>
+      <c r="AW10" s="45"/>
+      <c r="AX10" s="45"/>
+      <c r="AY10" s="45"/>
+      <c r="AZ10" s="45"/>
+      <c r="BA10" s="45"/>
+      <c r="BB10" s="45"/>
+      <c r="BC10" s="45"/>
+      <c r="BD10" s="45"/>
+      <c r="BE10" s="45"/>
+      <c r="BF10" s="45"/>
+      <c r="BG10" s="45"/>
+      <c r="BH10" s="45"/>
+      <c r="BI10" s="45"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="37"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="37"/>
-      <c r="AD11" s="37"/>
-      <c r="AE11" s="37"/>
-      <c r="AF11" s="37"/>
-      <c r="AG11" s="37"/>
-      <c r="AH11" s="37"/>
-      <c r="AI11" s="37"/>
-      <c r="AJ11" s="37"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="37"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="37"/>
-      <c r="AQ11" s="37"/>
-      <c r="AR11" s="37"/>
-      <c r="AS11" s="37"/>
-      <c r="AT11" s="37"/>
-      <c r="AU11" s="37"/>
-      <c r="AV11" s="37"/>
-      <c r="AW11" s="37"/>
-      <c r="AX11" s="37"/>
-      <c r="AY11" s="37"/>
-      <c r="AZ11" s="37"/>
-      <c r="BA11" s="37"/>
-      <c r="BB11" s="37"/>
-      <c r="BC11" s="37"/>
-      <c r="BD11" s="37"/>
-      <c r="BE11" s="37"/>
-      <c r="BF11" s="37"/>
-      <c r="BG11" s="37"/>
-      <c r="BH11" s="37"/>
-      <c r="BI11" s="37"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="45"/>
+      <c r="S11" s="45"/>
+      <c r="T11" s="45"/>
+      <c r="U11" s="45"/>
+      <c r="V11" s="45"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="45"/>
+      <c r="Y11" s="45"/>
+      <c r="Z11" s="45"/>
+      <c r="AA11" s="45"/>
+      <c r="AB11" s="45"/>
+      <c r="AC11" s="45"/>
+      <c r="AD11" s="45"/>
+      <c r="AE11" s="45"/>
+      <c r="AF11" s="45"/>
+      <c r="AG11" s="45"/>
+      <c r="AH11" s="45"/>
+      <c r="AI11" s="45"/>
+      <c r="AJ11" s="45"/>
+      <c r="AK11" s="45"/>
+      <c r="AL11" s="45"/>
+      <c r="AM11" s="45"/>
+      <c r="AN11" s="45"/>
+      <c r="AO11" s="45"/>
+      <c r="AP11" s="45"/>
+      <c r="AQ11" s="45"/>
+      <c r="AR11" s="45"/>
+      <c r="AS11" s="45"/>
+      <c r="AT11" s="45"/>
+      <c r="AU11" s="45"/>
+      <c r="AV11" s="45"/>
+      <c r="AW11" s="45"/>
+      <c r="AX11" s="45"/>
+      <c r="AY11" s="45"/>
+      <c r="AZ11" s="45"/>
+      <c r="BA11" s="45"/>
+      <c r="BB11" s="45"/>
+      <c r="BC11" s="45"/>
+      <c r="BD11" s="45"/>
+      <c r="BE11" s="45"/>
+      <c r="BF11" s="45"/>
+      <c r="BG11" s="45"/>
+      <c r="BH11" s="45"/>
+      <c r="BI11" s="45"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="36"/>
-      <c r="AD13" s="36"/>
-      <c r="AE13" s="36"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="36"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="36"/>
-      <c r="AK13" s="36"/>
-      <c r="AL13" s="36"/>
-      <c r="AM13" s="36"/>
-      <c r="AN13" s="36"/>
-      <c r="AO13" s="36"/>
-      <c r="AP13" s="36"/>
-      <c r="AQ13" s="36"/>
-      <c r="AR13" s="36"/>
-      <c r="AS13" s="36"/>
-      <c r="AT13" s="36"/>
-      <c r="AU13" s="36"/>
-      <c r="AV13" s="36"/>
-      <c r="AW13" s="36"/>
-      <c r="AX13" s="36"/>
-      <c r="AY13" s="36"/>
-      <c r="AZ13" s="36"/>
-      <c r="BA13" s="36"/>
-      <c r="BB13" s="36"/>
-      <c r="BC13" s="36"/>
-      <c r="BD13" s="36"/>
-      <c r="BE13" s="36"/>
-      <c r="BF13" s="36"/>
-      <c r="BG13" s="36"/>
-      <c r="BH13" s="36"/>
-      <c r="BI13" s="36"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="40"/>
+      <c r="AG13" s="40"/>
+      <c r="AH13" s="40"/>
+      <c r="AI13" s="40"/>
+      <c r="AJ13" s="40"/>
+      <c r="AK13" s="40"/>
+      <c r="AL13" s="40"/>
+      <c r="AM13" s="40"/>
+      <c r="AN13" s="40"/>
+      <c r="AO13" s="40"/>
+      <c r="AP13" s="40"/>
+      <c r="AQ13" s="40"/>
+      <c r="AR13" s="40"/>
+      <c r="AS13" s="40"/>
+      <c r="AT13" s="40"/>
+      <c r="AU13" s="40"/>
+      <c r="AV13" s="40"/>
+      <c r="AW13" s="40"/>
+      <c r="AX13" s="40"/>
+      <c r="AY13" s="40"/>
+      <c r="AZ13" s="40"/>
+      <c r="BA13" s="40"/>
+      <c r="BB13" s="40"/>
+      <c r="BC13" s="40"/>
+      <c r="BD13" s="40"/>
+      <c r="BE13" s="40"/>
+      <c r="BF13" s="40"/>
+      <c r="BG13" s="40"/>
+      <c r="BH13" s="40"/>
+      <c r="BI13" s="40"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="35" t="s">
-        <v>51</v>
+      <c r="A14" s="46" t="s">
+        <v>47</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="35"/>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="35"/>
-      <c r="AC14" s="35"/>
-      <c r="AD14" s="35"/>
-      <c r="AE14" s="35"/>
-      <c r="AF14" s="35"/>
-      <c r="AG14" s="35"/>
-      <c r="AH14" s="35"/>
-      <c r="AI14" s="35"/>
-      <c r="AJ14" s="35"/>
-      <c r="AK14" s="35"/>
-      <c r="AL14" s="35"/>
-      <c r="AM14" s="35"/>
-      <c r="AN14" s="35"/>
-      <c r="AO14" s="35"/>
-      <c r="AP14" s="35"/>
-      <c r="AQ14" s="35"/>
-      <c r="AR14" s="35"/>
-      <c r="AS14" s="35"/>
-      <c r="AT14" s="35"/>
-      <c r="AU14" s="35"/>
-      <c r="AV14" s="35"/>
-      <c r="AW14" s="35"/>
-      <c r="AX14" s="35"/>
-      <c r="AY14" s="35"/>
-      <c r="AZ14" s="35"/>
-      <c r="BA14" s="35"/>
-      <c r="BB14" s="35"/>
-      <c r="BC14" s="35"/>
-      <c r="BD14" s="35"/>
-      <c r="BE14" s="35"/>
-      <c r="BF14" s="35"/>
-      <c r="BG14" s="35"/>
-      <c r="BH14" s="35"/>
-      <c r="BI14" s="35"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="46"/>
+      <c r="Y14" s="46"/>
+      <c r="Z14" s="46"/>
+      <c r="AA14" s="46"/>
+      <c r="AB14" s="46"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="46"/>
+      <c r="AE14" s="46"/>
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="46"/>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="46"/>
+      <c r="AJ14" s="46"/>
+      <c r="AK14" s="46"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="46"/>
+      <c r="AN14" s="46"/>
+      <c r="AO14" s="46"/>
+      <c r="AP14" s="46"/>
+      <c r="AQ14" s="46"/>
+      <c r="AR14" s="46"/>
+      <c r="AS14" s="46"/>
+      <c r="AT14" s="46"/>
+      <c r="AU14" s="46"/>
+      <c r="AV14" s="46"/>
+      <c r="AW14" s="46"/>
+      <c r="AX14" s="46"/>
+      <c r="AY14" s="46"/>
+      <c r="AZ14" s="46"/>
+      <c r="BA14" s="46"/>
+      <c r="BB14" s="46"/>
+      <c r="BC14" s="46"/>
+      <c r="BD14" s="46"/>
+      <c r="BE14" s="46"/>
+      <c r="BF14" s="46"/>
+      <c r="BG14" s="46"/>
+      <c r="BH14" s="46"/>
+      <c r="BI14" s="46"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="35"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="35"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="35"/>
-      <c r="AL15" s="35"/>
-      <c r="AM15" s="35"/>
-      <c r="AN15" s="35"/>
-      <c r="AO15" s="35"/>
-      <c r="AP15" s="35"/>
-      <c r="AQ15" s="35"/>
-      <c r="AR15" s="35"/>
-      <c r="AS15" s="35"/>
-      <c r="AT15" s="35"/>
-      <c r="AU15" s="35"/>
-      <c r="AV15" s="35"/>
-      <c r="AW15" s="35"/>
-      <c r="AX15" s="35"/>
-      <c r="AY15" s="35"/>
-      <c r="AZ15" s="35"/>
-      <c r="BA15" s="35"/>
-      <c r="BB15" s="35"/>
-      <c r="BC15" s="35"/>
-      <c r="BD15" s="35"/>
-      <c r="BE15" s="35"/>
-      <c r="BF15" s="35"/>
-      <c r="BG15" s="35"/>
-      <c r="BH15" s="35"/>
-      <c r="BI15" s="35"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="46"/>
+      <c r="Y15" s="46"/>
+      <c r="Z15" s="46"/>
+      <c r="AA15" s="46"/>
+      <c r="AB15" s="46"/>
+      <c r="AC15" s="46"/>
+      <c r="AD15" s="46"/>
+      <c r="AE15" s="46"/>
+      <c r="AF15" s="46"/>
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="46"/>
+      <c r="AI15" s="46"/>
+      <c r="AJ15" s="46"/>
+      <c r="AK15" s="46"/>
+      <c r="AL15" s="46"/>
+      <c r="AM15" s="46"/>
+      <c r="AN15" s="46"/>
+      <c r="AO15" s="46"/>
+      <c r="AP15" s="46"/>
+      <c r="AQ15" s="46"/>
+      <c r="AR15" s="46"/>
+      <c r="AS15" s="46"/>
+      <c r="AT15" s="46"/>
+      <c r="AU15" s="46"/>
+      <c r="AV15" s="46"/>
+      <c r="AW15" s="46"/>
+      <c r="AX15" s="46"/>
+      <c r="AY15" s="46"/>
+      <c r="AZ15" s="46"/>
+      <c r="BA15" s="46"/>
+      <c r="BB15" s="46"/>
+      <c r="BC15" s="46"/>
+      <c r="BD15" s="46"/>
+      <c r="BE15" s="46"/>
+      <c r="BF15" s="46"/>
+      <c r="BG15" s="46"/>
+      <c r="BH15" s="46"/>
+      <c r="BI15" s="46"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="35"/>
-      <c r="AE16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="35"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="35"/>
-      <c r="AJ16" s="35"/>
-      <c r="AK16" s="35"/>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
-      <c r="AS16" s="35"/>
-      <c r="AT16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="35"/>
-      <c r="AX16" s="35"/>
-      <c r="AY16" s="35"/>
-      <c r="AZ16" s="35"/>
-      <c r="BA16" s="35"/>
-      <c r="BB16" s="35"/>
-      <c r="BC16" s="35"/>
-      <c r="BD16" s="35"/>
-      <c r="BE16" s="35"/>
-      <c r="BF16" s="35"/>
-      <c r="BG16" s="35"/>
-      <c r="BH16" s="35"/>
-      <c r="BI16" s="35"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="46"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="46"/>
+      <c r="AA16" s="46"/>
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="46"/>
+      <c r="AD16" s="46"/>
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="46"/>
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="46"/>
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="46"/>
+      <c r="AK16" s="46"/>
+      <c r="AL16" s="46"/>
+      <c r="AM16" s="46"/>
+      <c r="AN16" s="46"/>
+      <c r="AO16" s="46"/>
+      <c r="AP16" s="46"/>
+      <c r="AQ16" s="46"/>
+      <c r="AR16" s="46"/>
+      <c r="AS16" s="46"/>
+      <c r="AT16" s="46"/>
+      <c r="AU16" s="46"/>
+      <c r="AV16" s="46"/>
+      <c r="AW16" s="46"/>
+      <c r="AX16" s="46"/>
+      <c r="AY16" s="46"/>
+      <c r="AZ16" s="46"/>
+      <c r="BA16" s="46"/>
+      <c r="BB16" s="46"/>
+      <c r="BC16" s="46"/>
+      <c r="BD16" s="46"/>
+      <c r="BE16" s="46"/>
+      <c r="BF16" s="46"/>
+      <c r="BG16" s="46"/>
+      <c r="BH16" s="46"/>
+      <c r="BI16" s="46"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="35"/>
-      <c r="AC17" s="35"/>
-      <c r="AD17" s="35"/>
-      <c r="AE17" s="35"/>
-      <c r="AF17" s="35"/>
-      <c r="AG17" s="35"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="35"/>
-      <c r="AJ17" s="35"/>
-      <c r="AK17" s="35"/>
-      <c r="AL17" s="35"/>
-      <c r="AM17" s="35"/>
-      <c r="AN17" s="35"/>
-      <c r="AO17" s="35"/>
-      <c r="AP17" s="35"/>
-      <c r="AQ17" s="35"/>
-      <c r="AR17" s="35"/>
-      <c r="AS17" s="35"/>
-      <c r="AT17" s="35"/>
-      <c r="AU17" s="35"/>
-      <c r="AV17" s="35"/>
-      <c r="AW17" s="35"/>
-      <c r="AX17" s="35"/>
-      <c r="AY17" s="35"/>
-      <c r="AZ17" s="35"/>
-      <c r="BA17" s="35"/>
-      <c r="BB17" s="35"/>
-      <c r="BC17" s="35"/>
-      <c r="BD17" s="35"/>
-      <c r="BE17" s="35"/>
-      <c r="BF17" s="35"/>
-      <c r="BG17" s="35"/>
-      <c r="BH17" s="35"/>
-      <c r="BI17" s="35"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="46"/>
+      <c r="AA17" s="46"/>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="46"/>
+      <c r="AF17" s="46"/>
+      <c r="AG17" s="46"/>
+      <c r="AH17" s="46"/>
+      <c r="AI17" s="46"/>
+      <c r="AJ17" s="46"/>
+      <c r="AK17" s="46"/>
+      <c r="AL17" s="46"/>
+      <c r="AM17" s="46"/>
+      <c r="AN17" s="46"/>
+      <c r="AO17" s="46"/>
+      <c r="AP17" s="46"/>
+      <c r="AQ17" s="46"/>
+      <c r="AR17" s="46"/>
+      <c r="AS17" s="46"/>
+      <c r="AT17" s="46"/>
+      <c r="AU17" s="46"/>
+      <c r="AV17" s="46"/>
+      <c r="AW17" s="46"/>
+      <c r="AX17" s="46"/>
+      <c r="AY17" s="46"/>
+      <c r="AZ17" s="46"/>
+      <c r="BA17" s="46"/>
+      <c r="BB17" s="46"/>
+      <c r="BC17" s="46"/>
+      <c r="BD17" s="46"/>
+      <c r="BE17" s="46"/>
+      <c r="BF17" s="46"/>
+      <c r="BG17" s="46"/>
+      <c r="BH17" s="46"/>
+      <c r="BI17" s="46"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="35"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="35"/>
-      <c r="AC18" s="35"/>
-      <c r="AD18" s="35"/>
-      <c r="AE18" s="35"/>
-      <c r="AF18" s="35"/>
-      <c r="AG18" s="35"/>
-      <c r="AH18" s="35"/>
-      <c r="AI18" s="35"/>
-      <c r="AJ18" s="35"/>
-      <c r="AK18" s="35"/>
-      <c r="AL18" s="35"/>
-      <c r="AM18" s="35"/>
-      <c r="AN18" s="35"/>
-      <c r="AO18" s="35"/>
-      <c r="AP18" s="35"/>
-      <c r="AQ18" s="35"/>
-      <c r="AR18" s="35"/>
-      <c r="AS18" s="35"/>
-      <c r="AT18" s="35"/>
-      <c r="AU18" s="35"/>
-      <c r="AV18" s="35"/>
-      <c r="AW18" s="35"/>
-      <c r="AX18" s="35"/>
-      <c r="AY18" s="35"/>
-      <c r="AZ18" s="35"/>
-      <c r="BA18" s="35"/>
-      <c r="BB18" s="35"/>
-      <c r="BC18" s="35"/>
-      <c r="BD18" s="35"/>
-      <c r="BE18" s="35"/>
-      <c r="BF18" s="35"/>
-      <c r="BG18" s="35"/>
-      <c r="BH18" s="35"/>
-      <c r="BI18" s="35"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="46"/>
+      <c r="Y18" s="46"/>
+      <c r="Z18" s="46"/>
+      <c r="AA18" s="46"/>
+      <c r="AB18" s="46"/>
+      <c r="AC18" s="46"/>
+      <c r="AD18" s="46"/>
+      <c r="AE18" s="46"/>
+      <c r="AF18" s="46"/>
+      <c r="AG18" s="46"/>
+      <c r="AH18" s="46"/>
+      <c r="AI18" s="46"/>
+      <c r="AJ18" s="46"/>
+      <c r="AK18" s="46"/>
+      <c r="AL18" s="46"/>
+      <c r="AM18" s="46"/>
+      <c r="AN18" s="46"/>
+      <c r="AO18" s="46"/>
+      <c r="AP18" s="46"/>
+      <c r="AQ18" s="46"/>
+      <c r="AR18" s="46"/>
+      <c r="AS18" s="46"/>
+      <c r="AT18" s="46"/>
+      <c r="AU18" s="46"/>
+      <c r="AV18" s="46"/>
+      <c r="AW18" s="46"/>
+      <c r="AX18" s="46"/>
+      <c r="AY18" s="46"/>
+      <c r="AZ18" s="46"/>
+      <c r="BA18" s="46"/>
+      <c r="BB18" s="46"/>
+      <c r="BC18" s="46"/>
+      <c r="BD18" s="46"/>
+      <c r="BE18" s="46"/>
+      <c r="BF18" s="46"/>
+      <c r="BG18" s="46"/>
+      <c r="BH18" s="46"/>
+      <c r="BI18" s="46"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="35"/>
-      <c r="AC19" s="35"/>
-      <c r="AD19" s="35"/>
-      <c r="AE19" s="35"/>
-      <c r="AF19" s="35"/>
-      <c r="AG19" s="35"/>
-      <c r="AH19" s="35"/>
-      <c r="AI19" s="35"/>
-      <c r="AJ19" s="35"/>
-      <c r="AK19" s="35"/>
-      <c r="AL19" s="35"/>
-      <c r="AM19" s="35"/>
-      <c r="AN19" s="35"/>
-      <c r="AO19" s="35"/>
-      <c r="AP19" s="35"/>
-      <c r="AQ19" s="35"/>
-      <c r="AR19" s="35"/>
-      <c r="AS19" s="35"/>
-      <c r="AT19" s="35"/>
-      <c r="AU19" s="35"/>
-      <c r="AV19" s="35"/>
-      <c r="AW19" s="35"/>
-      <c r="AX19" s="35"/>
-      <c r="AY19" s="35"/>
-      <c r="AZ19" s="35"/>
-      <c r="BA19" s="35"/>
-      <c r="BB19" s="35"/>
-      <c r="BC19" s="35"/>
-      <c r="BD19" s="35"/>
-      <c r="BE19" s="35"/>
-      <c r="BF19" s="35"/>
-      <c r="BG19" s="35"/>
-      <c r="BH19" s="35"/>
-      <c r="BI19" s="35"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="46"/>
+      <c r="X19" s="46"/>
+      <c r="Y19" s="46"/>
+      <c r="Z19" s="46"/>
+      <c r="AA19" s="46"/>
+      <c r="AB19" s="46"/>
+      <c r="AC19" s="46"/>
+      <c r="AD19" s="46"/>
+      <c r="AE19" s="46"/>
+      <c r="AF19" s="46"/>
+      <c r="AG19" s="46"/>
+      <c r="AH19" s="46"/>
+      <c r="AI19" s="46"/>
+      <c r="AJ19" s="46"/>
+      <c r="AK19" s="46"/>
+      <c r="AL19" s="46"/>
+      <c r="AM19" s="46"/>
+      <c r="AN19" s="46"/>
+      <c r="AO19" s="46"/>
+      <c r="AP19" s="46"/>
+      <c r="AQ19" s="46"/>
+      <c r="AR19" s="46"/>
+      <c r="AS19" s="46"/>
+      <c r="AT19" s="46"/>
+      <c r="AU19" s="46"/>
+      <c r="AV19" s="46"/>
+      <c r="AW19" s="46"/>
+      <c r="AX19" s="46"/>
+      <c r="AY19" s="46"/>
+      <c r="AZ19" s="46"/>
+      <c r="BA19" s="46"/>
+      <c r="BB19" s="46"/>
+      <c r="BC19" s="46"/>
+      <c r="BD19" s="46"/>
+      <c r="BE19" s="46"/>
+      <c r="BF19" s="46"/>
+      <c r="BG19" s="46"/>
+      <c r="BH19" s="46"/>
+      <c r="BI19" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="A14:BI19"/>
+    <mergeCell ref="A13:BI13"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:AD10"/>
+    <mergeCell ref="AE10:AN10"/>
+    <mergeCell ref="AO10:BI10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="U11:AD11"/>
+    <mergeCell ref="AE11:AN11"/>
+    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="K9:T9"/>
+    <mergeCell ref="U9:AD9"/>
+    <mergeCell ref="AE9:AN9"/>
+    <mergeCell ref="AO9:BI9"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
@@ -2911,29 +2910,14 @@
     <mergeCell ref="R2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:T9"/>
-    <mergeCell ref="U9:AD9"/>
-    <mergeCell ref="AE9:AN9"/>
-    <mergeCell ref="AO9:BI9"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="A14:BI19"/>
-    <mergeCell ref="A13:BI13"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:T10"/>
-    <mergeCell ref="U10:AD10"/>
-    <mergeCell ref="AE10:AN10"/>
-    <mergeCell ref="AO10:BI10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:T11"/>
-    <mergeCell ref="U11:AD11"/>
-    <mergeCell ref="AE11:AN11"/>
-    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2945,7 +2929,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IX54"/>
+  <dimension ref="A1:IX52"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
@@ -2966,72 +2950,72 @@
       <c r="J1" s="42"/>
       <c r="K1" s="42"/>
       <c r="L1" s="42"/>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="43" t="s">
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="44" t="s">
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="43" t="str">
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="36" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="43"/>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="43"/>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="44" t="s">
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="44"/>
-      <c r="AS1" s="44"/>
-      <c r="AT1" s="43" t="s">
+      <c r="AR1" s="35"/>
+      <c r="AS1" s="35"/>
+      <c r="AT1" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="43"/>
-      <c r="AV1" s="43"/>
-      <c r="AW1" s="43"/>
-      <c r="AX1" s="43"/>
-      <c r="AY1" s="43"/>
-      <c r="AZ1" s="43"/>
-      <c r="BA1" s="44" t="s">
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
+      <c r="AY1" s="36"/>
+      <c r="AZ1" s="36"/>
+      <c r="BA1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="44"/>
-      <c r="BC1" s="44"/>
-      <c r="BD1" s="45">
+      <c r="BB1" s="35"/>
+      <c r="BC1" s="35"/>
+      <c r="BD1" s="43">
         <v>45555</v>
       </c>
-      <c r="BE1" s="45"/>
-      <c r="BF1" s="45"/>
-      <c r="BG1" s="45"/>
-      <c r="BH1" s="45"/>
-      <c r="BI1" s="45"/>
+      <c r="BE1" s="43"/>
+      <c r="BF1" s="43"/>
+      <c r="BG1" s="43"/>
+      <c r="BH1" s="43"/>
+      <c r="BI1" s="43"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3243,70 +3227,70 @@
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
       <c r="L2" s="42"/>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="44" t="s">
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="43" t="str">
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="36" t="str">
         <f>クラス仕様!G5</f>
         <v>PagingUtil</v>
       </c>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="43"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43"/>
-      <c r="AQ2" s="44" t="s">
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="44"/>
-      <c r="AS2" s="44"/>
-      <c r="AT2" s="43" t="s">
-        <v>50</v>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="36" t="s">
+        <v>46</v>
       </c>
-      <c r="AU2" s="43"/>
-      <c r="AV2" s="43"/>
-      <c r="AW2" s="43"/>
-      <c r="AX2" s="43"/>
-      <c r="AY2" s="43"/>
-      <c r="AZ2" s="43"/>
-      <c r="BA2" s="44" t="s">
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="44"/>
-      <c r="BC2" s="44"/>
-      <c r="BD2" s="39">
-        <v>45587</v>
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="37">
+        <v>45589</v>
       </c>
-      <c r="BE2" s="40"/>
-      <c r="BF2" s="40"/>
-      <c r="BG2" s="40"/>
-      <c r="BH2" s="40"/>
-      <c r="BI2" s="41"/>
+      <c r="BE2" s="38"/>
+      <c r="BF2" s="38"/>
+      <c r="BG2" s="38"/>
+      <c r="BH2" s="38"/>
+      <c r="BI2" s="39"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3569,71 +3553,71 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="38" t="s">
-        <v>53</v>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41" t="s">
+        <v>49</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="41"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="41"/>
+      <c r="BG4" s="41"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="41"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -3833,71 +3817,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="41"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="41"/>
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="41"/>
+      <c r="BG5" s="41"/>
+      <c r="BH5" s="41"/>
+      <c r="BI5" s="41"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -4357,75 +4341,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49" t="s">
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="49"/>
-      <c r="AD7" s="49"/>
-      <c r="AE7" s="49" t="s">
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="50"/>
+      <c r="AA7" s="50"/>
+      <c r="AB7" s="50"/>
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="50"/>
+      <c r="AE7" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="49"/>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="49"/>
-      <c r="AJ7" s="49"/>
-      <c r="AK7" s="49"/>
-      <c r="AL7" s="49"/>
-      <c r="AM7" s="49"/>
-      <c r="AN7" s="49"/>
-      <c r="AO7" s="49"/>
-      <c r="AP7" s="49"/>
-      <c r="AQ7" s="49"/>
-      <c r="AR7" s="49"/>
-      <c r="AS7" s="49"/>
-      <c r="AT7" s="49"/>
-      <c r="AU7" s="49"/>
-      <c r="AV7" s="49"/>
-      <c r="AW7" s="49"/>
-      <c r="AX7" s="49"/>
-      <c r="AY7" s="49"/>
-      <c r="AZ7" s="49"/>
-      <c r="BA7" s="49"/>
-      <c r="BB7" s="49"/>
-      <c r="BC7" s="49"/>
-      <c r="BD7" s="49"/>
-      <c r="BE7" s="49"/>
-      <c r="BF7" s="49"/>
-      <c r="BG7" s="49"/>
-      <c r="BH7" s="49"/>
-      <c r="BI7" s="49"/>
+      <c r="AF7" s="50"/>
+      <c r="AG7" s="50"/>
+      <c r="AH7" s="50"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="50"/>
+      <c r="AK7" s="50"/>
+      <c r="AL7" s="50"/>
+      <c r="AM7" s="50"/>
+      <c r="AN7" s="50"/>
+      <c r="AO7" s="50"/>
+      <c r="AP7" s="50"/>
+      <c r="AQ7" s="50"/>
+      <c r="AR7" s="50"/>
+      <c r="AS7" s="50"/>
+      <c r="AT7" s="50"/>
+      <c r="AU7" s="50"/>
+      <c r="AV7" s="50"/>
+      <c r="AW7" s="50"/>
+      <c r="AX7" s="50"/>
+      <c r="AY7" s="50"/>
+      <c r="AZ7" s="50"/>
+      <c r="BA7" s="50"/>
+      <c r="BB7" s="50"/>
+      <c r="BC7" s="50"/>
+      <c r="BD7" s="50"/>
+      <c r="BE7" s="50"/>
+      <c r="BF7" s="50"/>
+      <c r="BG7" s="50"/>
+      <c r="BH7" s="50"/>
+      <c r="BI7" s="50"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4625,75 +4609,75 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="53" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="53" t="s">
-        <v>48</v>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="47" t="s">
+        <v>44</v>
       </c>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="54"/>
-      <c r="Z8" s="54"/>
-      <c r="AA8" s="54"/>
-      <c r="AB8" s="54"/>
-      <c r="AC8" s="54"/>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="53" t="s">
-        <v>54</v>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
+      <c r="Z8" s="48"/>
+      <c r="AA8" s="48"/>
+      <c r="AB8" s="48"/>
+      <c r="AC8" s="48"/>
+      <c r="AD8" s="49"/>
+      <c r="AE8" s="47" t="s">
+        <v>50</v>
       </c>
-      <c r="AF8" s="54"/>
-      <c r="AG8" s="54"/>
-      <c r="AH8" s="54"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="54"/>
-      <c r="AK8" s="54"/>
-      <c r="AL8" s="54"/>
-      <c r="AM8" s="54"/>
-      <c r="AN8" s="54"/>
-      <c r="AO8" s="54"/>
-      <c r="AP8" s="54"/>
-      <c r="AQ8" s="54"/>
-      <c r="AR8" s="54"/>
-      <c r="AS8" s="54"/>
-      <c r="AT8" s="54"/>
-      <c r="AU8" s="54"/>
-      <c r="AV8" s="54"/>
-      <c r="AW8" s="54"/>
-      <c r="AX8" s="54"/>
-      <c r="AY8" s="54"/>
-      <c r="AZ8" s="54"/>
-      <c r="BA8" s="54"/>
-      <c r="BB8" s="54"/>
-      <c r="BC8" s="54"/>
-      <c r="BD8" s="54"/>
-      <c r="BE8" s="54"/>
-      <c r="BF8" s="54"/>
-      <c r="BG8" s="54"/>
-      <c r="BH8" s="54"/>
-      <c r="BI8" s="55"/>
+      <c r="AF8" s="48"/>
+      <c r="AG8" s="48"/>
+      <c r="AH8" s="48"/>
+      <c r="AI8" s="48"/>
+      <c r="AJ8" s="48"/>
+      <c r="AK8" s="48"/>
+      <c r="AL8" s="48"/>
+      <c r="AM8" s="48"/>
+      <c r="AN8" s="48"/>
+      <c r="AO8" s="48"/>
+      <c r="AP8" s="48"/>
+      <c r="AQ8" s="48"/>
+      <c r="AR8" s="48"/>
+      <c r="AS8" s="48"/>
+      <c r="AT8" s="48"/>
+      <c r="AU8" s="48"/>
+      <c r="AV8" s="48"/>
+      <c r="AW8" s="48"/>
+      <c r="AX8" s="48"/>
+      <c r="AY8" s="48"/>
+      <c r="AZ8" s="48"/>
+      <c r="BA8" s="48"/>
+      <c r="BB8" s="48"/>
+      <c r="BC8" s="48"/>
+      <c r="BD8" s="48"/>
+      <c r="BE8" s="48"/>
+      <c r="BF8" s="48"/>
+      <c r="BG8" s="48"/>
+      <c r="BH8" s="48"/>
+      <c r="BI8" s="49"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -4893,75 +4877,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48" t="s">
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="48" t="s">
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="48"/>
-      <c r="AE9" s="48" t="s">
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="52"/>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="48"/>
-      <c r="AH9" s="48"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="48"/>
-      <c r="AK9" s="48"/>
-      <c r="AL9" s="48"/>
-      <c r="AM9" s="48"/>
-      <c r="AN9" s="48"/>
-      <c r="AO9" s="48"/>
-      <c r="AP9" s="48"/>
-      <c r="AQ9" s="48"/>
-      <c r="AR9" s="48"/>
-      <c r="AS9" s="48"/>
-      <c r="AT9" s="48"/>
-      <c r="AU9" s="48"/>
-      <c r="AV9" s="48"/>
-      <c r="AW9" s="48"/>
-      <c r="AX9" s="48"/>
-      <c r="AY9" s="48"/>
-      <c r="AZ9" s="48"/>
-      <c r="BA9" s="48"/>
-      <c r="BB9" s="48"/>
-      <c r="BC9" s="48"/>
-      <c r="BD9" s="48"/>
-      <c r="BE9" s="48"/>
-      <c r="BF9" s="48"/>
-      <c r="BG9" s="48"/>
-      <c r="BH9" s="48"/>
-      <c r="BI9" s="48"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="52"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="52"/>
+      <c r="AK9" s="52"/>
+      <c r="AL9" s="52"/>
+      <c r="AM9" s="52"/>
+      <c r="AN9" s="52"/>
+      <c r="AO9" s="52"/>
+      <c r="AP9" s="52"/>
+      <c r="AQ9" s="52"/>
+      <c r="AR9" s="52"/>
+      <c r="AS9" s="52"/>
+      <c r="AT9" s="52"/>
+      <c r="AU9" s="52"/>
+      <c r="AV9" s="52"/>
+      <c r="AW9" s="52"/>
+      <c r="AX9" s="52"/>
+      <c r="AY9" s="52"/>
+      <c r="AZ9" s="52"/>
+      <c r="BA9" s="52"/>
+      <c r="BB9" s="52"/>
+      <c r="BC9" s="52"/>
+      <c r="BD9" s="52"/>
+      <c r="BE9" s="52"/>
+      <c r="BF9" s="52"/>
+      <c r="BG9" s="52"/>
+      <c r="BH9" s="52"/>
+      <c r="BI9" s="52"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -5161,71 +5145,71 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37" t="s">
-        <v>55</v>
+      <c r="A10" s="45" t="s">
+        <v>51</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="50" t="s">
-        <v>56</v>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="53" t="s">
+        <v>52</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="51"/>
-      <c r="Z10" s="51"/>
-      <c r="AA10" s="51"/>
-      <c r="AB10" s="51"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="51"/>
-      <c r="AE10" s="51"/>
-      <c r="AF10" s="51"/>
-      <c r="AG10" s="51"/>
-      <c r="AH10" s="51"/>
-      <c r="AI10" s="51"/>
-      <c r="AJ10" s="51"/>
-      <c r="AK10" s="51"/>
-      <c r="AL10" s="51"/>
-      <c r="AM10" s="51"/>
-      <c r="AN10" s="51"/>
-      <c r="AO10" s="51"/>
-      <c r="AP10" s="51"/>
-      <c r="AQ10" s="51"/>
-      <c r="AR10" s="51"/>
-      <c r="AS10" s="51"/>
-      <c r="AT10" s="51"/>
-      <c r="AU10" s="51"/>
-      <c r="AV10" s="51"/>
-      <c r="AW10" s="51"/>
-      <c r="AX10" s="51"/>
-      <c r="AY10" s="51"/>
-      <c r="AZ10" s="51"/>
-      <c r="BA10" s="51"/>
-      <c r="BB10" s="51"/>
-      <c r="BC10" s="51"/>
-      <c r="BD10" s="51"/>
-      <c r="BE10" s="51"/>
-      <c r="BF10" s="51"/>
-      <c r="BG10" s="51"/>
-      <c r="BH10" s="51"/>
-      <c r="BI10" s="52"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="54"/>
+      <c r="AG10" s="54"/>
+      <c r="AH10" s="54"/>
+      <c r="AI10" s="54"/>
+      <c r="AJ10" s="54"/>
+      <c r="AK10" s="54"/>
+      <c r="AL10" s="54"/>
+      <c r="AM10" s="54"/>
+      <c r="AN10" s="54"/>
+      <c r="AO10" s="54"/>
+      <c r="AP10" s="54"/>
+      <c r="AQ10" s="54"/>
+      <c r="AR10" s="54"/>
+      <c r="AS10" s="54"/>
+      <c r="AT10" s="54"/>
+      <c r="AU10" s="54"/>
+      <c r="AV10" s="54"/>
+      <c r="AW10" s="54"/>
+      <c r="AX10" s="54"/>
+      <c r="AY10" s="54"/>
+      <c r="AZ10" s="54"/>
+      <c r="BA10" s="54"/>
+      <c r="BB10" s="54"/>
+      <c r="BC10" s="54"/>
+      <c r="BD10" s="54"/>
+      <c r="BE10" s="54"/>
+      <c r="BF10" s="54"/>
+      <c r="BG10" s="54"/>
+      <c r="BH10" s="54"/>
+      <c r="BI10" s="55"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5685,73 +5669,73 @@
       <c r="IX11" s="1"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49" t="s">
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="49"/>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="49"/>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
-      <c r="AP12" s="49"/>
-      <c r="AQ12" s="49"/>
-      <c r="AR12" s="49"/>
-      <c r="AS12" s="49"/>
-      <c r="AT12" s="49" t="s">
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="50"/>
+      <c r="AE12" s="50"/>
+      <c r="AF12" s="50"/>
+      <c r="AG12" s="50"/>
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="50"/>
+      <c r="AK12" s="50"/>
+      <c r="AL12" s="50"/>
+      <c r="AM12" s="50"/>
+      <c r="AN12" s="50"/>
+      <c r="AO12" s="50"/>
+      <c r="AP12" s="50"/>
+      <c r="AQ12" s="50"/>
+      <c r="AR12" s="50"/>
+      <c r="AS12" s="50"/>
+      <c r="AT12" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="AU12" s="49"/>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
-      <c r="BB12" s="49"/>
-      <c r="BC12" s="49"/>
-      <c r="BD12" s="49"/>
-      <c r="BE12" s="49"/>
-      <c r="BF12" s="49"/>
-      <c r="BG12" s="49"/>
-      <c r="BH12" s="49"/>
-      <c r="BI12" s="49"/>
+      <c r="AU12" s="50"/>
+      <c r="AV12" s="50"/>
+      <c r="AW12" s="50"/>
+      <c r="AX12" s="50"/>
+      <c r="AY12" s="50"/>
+      <c r="AZ12" s="50"/>
+      <c r="BA12" s="50"/>
+      <c r="BB12" s="50"/>
+      <c r="BC12" s="50"/>
+      <c r="BD12" s="50"/>
+      <c r="BE12" s="50"/>
+      <c r="BF12" s="50"/>
+      <c r="BG12" s="50"/>
+      <c r="BH12" s="50"/>
+      <c r="BI12" s="50"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
@@ -6214,7 +6198,7 @@
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -6232,7 +6216,7 @@
       <c r="O14" s="11"/>
       <c r="P14" s="33"/>
       <c r="Q14" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
@@ -6756,7 +6740,7 @@
       <c r="O16" s="11"/>
       <c r="P16" s="33"/>
       <c r="Q16" s="17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
@@ -7002,7 +6986,7 @@
     </row>
     <row r="17" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -7020,7 +7004,7 @@
       <c r="O17" s="11"/>
       <c r="P17" s="33"/>
       <c r="Q17" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
@@ -7282,7 +7266,7 @@
       <c r="O18" s="11"/>
       <c r="P18" s="33"/>
       <c r="Q18" s="17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
@@ -7528,7 +7512,7 @@
     </row>
     <row r="19" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -7546,7 +7530,7 @@
       <c r="O19" s="11"/>
       <c r="P19" s="33"/>
       <c r="Q19" s="17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
@@ -7808,7 +7792,7 @@
       <c r="O20" s="11"/>
       <c r="P20" s="16"/>
       <c r="Q20" s="17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
@@ -8070,7 +8054,7 @@
       <c r="O21" s="11"/>
       <c r="P21" s="16"/>
       <c r="Q21" s="17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
@@ -8591,7 +8575,7 @@
       <c r="N23" s="10"/>
       <c r="O23" s="11"/>
       <c r="P23" s="33" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
@@ -9115,7 +9099,7 @@
       <c r="P25" s="16"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="S25" s="19"/>
       <c r="T25" s="17"/>
@@ -9637,7 +9621,7 @@
       <c r="P27" s="16"/>
       <c r="Q27" s="19"/>
       <c r="R27" s="19" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="S27" s="19"/>
       <c r="T27" s="17"/>
@@ -9897,7 +9881,7 @@
       <c r="O28" s="11"/>
       <c r="P28" s="16"/>
       <c r="Q28" s="19" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="R28" s="19"/>
       <c r="S28" s="19"/>
@@ -10418,10 +10402,10 @@
       <c r="N30" s="10"/>
       <c r="O30" s="11"/>
       <c r="P30" s="16"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19" t="s">
+      <c r="Q30" s="19" t="s">
         <v>70</v>
       </c>
+      <c r="R30" s="19"/>
       <c r="S30" s="19"/>
       <c r="T30" s="17"/>
       <c r="U30" s="17"/>
@@ -10664,9 +10648,7 @@
       <c r="IX30" s="1"/>
     </row>
     <row r="31" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
@@ -10681,14 +10663,14 @@
       <c r="N31" s="10"/>
       <c r="O31" s="11"/>
       <c r="P31" s="16"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17" t="s">
-        <v>43</v>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19" t="s">
+        <v>71</v>
       </c>
+      <c r="S31" s="19"/>
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
-      <c r="V31" s="19"/>
+      <c r="V31" s="17"/>
       <c r="W31" s="17"/>
       <c r="X31" s="17"/>
       <c r="Y31" s="17"/>
@@ -10945,7 +10927,7 @@
       <c r="P32" s="16"/>
       <c r="Q32" s="17"/>
       <c r="R32" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S32" s="17"/>
       <c r="T32" s="17"/>
@@ -11208,7 +11190,7 @@
       <c r="Q33" s="21"/>
       <c r="R33" s="19"/>
       <c r="S33" s="19" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="T33" s="19"/>
       <c r="U33" s="22"/>
@@ -11470,7 +11452,7 @@
       <c r="Q34" s="21"/>
       <c r="R34" s="19"/>
       <c r="S34" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T34" s="19"/>
       <c r="U34" s="22"/>
@@ -11730,13 +11712,13 @@
       <c r="O35" s="11"/>
       <c r="P35" s="20"/>
       <c r="Q35" s="21"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17" t="s">
-        <v>79</v>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19" t="s">
+        <v>77</v>
       </c>
-      <c r="T35" s="17"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="19"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
       <c r="W35" s="17"/>
       <c r="X35" s="17"/>
       <c r="Y35" s="17"/>
@@ -11992,13 +11974,13 @@
       <c r="O36" s="11"/>
       <c r="P36" s="20"/>
       <c r="Q36" s="21"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17" t="s">
-        <v>45</v>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19" t="s">
+        <v>74</v>
       </c>
-      <c r="T36" s="17"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="19"/>
+      <c r="T36" s="19"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
       <c r="W36" s="17"/>
       <c r="X36" s="17"/>
       <c r="Y36" s="17"/>
@@ -12237,9 +12219,7 @@
       <c r="IX36" s="1"/>
     </row>
     <row r="37" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -12256,10 +12236,10 @@
       <c r="O37" s="11"/>
       <c r="P37" s="20"/>
       <c r="Q37" s="21"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19" t="s">
-        <v>80</v>
+      <c r="R37" s="19" t="s">
+        <v>73</v>
       </c>
+      <c r="S37" s="19"/>
       <c r="T37" s="19"/>
       <c r="U37" s="22"/>
       <c r="V37" s="22"/>
@@ -12518,13 +12498,13 @@
       <c r="O38" s="11"/>
       <c r="P38" s="20"/>
       <c r="Q38" s="21"/>
-      <c r="R38" s="19" t="s">
-        <v>72</v>
+      <c r="R38" s="17"/>
+      <c r="S38" s="19" t="s">
+        <v>78</v>
       </c>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="22"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="19"/>
+      <c r="V38" s="19"/>
       <c r="W38" s="17"/>
       <c r="X38" s="17"/>
       <c r="Y38" s="17"/>
@@ -12782,7 +12762,7 @@
       <c r="Q39" s="21"/>
       <c r="R39" s="17"/>
       <c r="S39" s="19" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="T39" s="17"/>
       <c r="U39" s="19"/>
@@ -13044,7 +13024,7 @@
       <c r="Q40" s="21"/>
       <c r="R40" s="17"/>
       <c r="S40" s="19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T40" s="17"/>
       <c r="U40" s="19"/>
@@ -13303,10 +13283,10 @@
       <c r="N41" s="10"/>
       <c r="O41" s="11"/>
       <c r="P41" s="20"/>
-      <c r="Q41" s="21"/>
+      <c r="Q41" s="19"/>
       <c r="R41" s="17"/>
-      <c r="S41" s="17" t="s">
-        <v>81</v>
+      <c r="S41" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="T41" s="17"/>
       <c r="U41" s="19"/>
@@ -13564,15 +13544,15 @@
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
       <c r="O42" s="11"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17" t="s">
-        <v>45</v>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="17" t="s">
+        <v>80</v>
       </c>
+      <c r="S42" s="17"/>
       <c r="T42" s="17"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="19"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
       <c r="W42" s="17"/>
       <c r="X42" s="17"/>
       <c r="Y42" s="17"/>
@@ -13811,9 +13791,7 @@
       <c r="IX42" s="1"/>
     </row>
     <row r="43" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -13832,13 +13810,13 @@
       <c r="Q43" s="17"/>
       <c r="R43" s="17"/>
       <c r="S43" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T43" s="17"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="19"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
       <c r="W43" s="17"/>
-      <c r="X43" s="17"/>
+      <c r="X43" s="19"/>
       <c r="Y43" s="17"/>
       <c r="Z43" s="17"/>
       <c r="AA43" s="17"/>
@@ -14091,11 +14069,11 @@
       <c r="N44" s="10"/>
       <c r="O44" s="11"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="23"/>
-      <c r="R44" s="17" t="s">
-        <v>73</v>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="19" t="s">
+        <v>82</v>
       </c>
-      <c r="S44" s="17"/>
       <c r="T44" s="17"/>
       <c r="U44" s="17"/>
       <c r="V44" s="17"/>
@@ -14338,12 +14316,6 @@
     </row>
     <row r="45" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -14356,13 +14328,13 @@
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
       <c r="S45" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T45" s="17"/>
       <c r="U45" s="17"/>
       <c r="V45" s="17"/>
       <c r="W45" s="17"/>
-      <c r="X45" s="19"/>
+      <c r="X45" s="17"/>
       <c r="Y45" s="17"/>
       <c r="Z45" s="17"/>
       <c r="AA45" s="17"/>
@@ -14386,7 +14358,7 @@
       <c r="AS45" s="18"/>
       <c r="AT45" s="8"/>
       <c r="AU45" s="10"/>
-      <c r="AV45" s="10"/>
+      <c r="AV45" s="9"/>
       <c r="AW45" s="10"/>
       <c r="AX45" s="10"/>
       <c r="AY45" s="10"/>
@@ -14599,8 +14571,10 @@
       <c r="IX45" s="1"/>
     </row>
     <row r="46" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
+      <c r="A46" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
@@ -14614,12 +14588,11 @@
       <c r="M46" s="10"/>
       <c r="N46" s="10"/>
       <c r="O46" s="11"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="17"/>
+      <c r="P46" s="34"/>
+      <c r="Q46" s="17" t="s">
+        <v>67</v>
+      </c>
       <c r="R46" s="17"/>
-      <c r="S46" s="19" t="s">
-        <v>83</v>
-      </c>
       <c r="T46" s="17"/>
       <c r="U46" s="17"/>
       <c r="V46" s="17"/>
@@ -14870,12 +14843,12 @@
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
       <c r="O47" s="11"/>
-      <c r="P47" s="16"/>
+      <c r="P47" s="33" t="s">
+        <v>57</v>
+      </c>
       <c r="Q47" s="17"/>
       <c r="R47" s="17"/>
-      <c r="S47" s="17" t="s">
-        <v>45</v>
-      </c>
+      <c r="S47" s="17"/>
       <c r="T47" s="17"/>
       <c r="U47" s="17"/>
       <c r="V47" s="17"/>
@@ -15117,15 +15090,7 @@
       <c r="IX47" s="1"/>
     </row>
     <row r="48" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
+      <c r="A48" s="8"/>
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -15134,12 +15099,12 @@
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
       <c r="O48" s="11"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="17"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="17" t="s">
+        <v>65</v>
+      </c>
       <c r="R48" s="17"/>
-      <c r="S48" s="17" t="s">
-        <v>84</v>
-      </c>
+      <c r="S48" s="17"/>
       <c r="T48" s="17"/>
       <c r="U48" s="17"/>
       <c r="V48" s="17"/>
@@ -15168,7 +15133,7 @@
       <c r="AS48" s="18"/>
       <c r="AT48" s="8"/>
       <c r="AU48" s="10"/>
-      <c r="AV48" s="10"/>
+      <c r="AV48" s="9"/>
       <c r="AW48" s="10"/>
       <c r="AX48" s="10"/>
       <c r="AY48" s="10"/>
@@ -15390,10 +15355,10 @@
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
       <c r="O49" s="11"/>
-      <c r="P49" s="33" t="s">
-        <v>61</v>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="17" t="s">
+        <v>43</v>
       </c>
-      <c r="Q49" s="17"/>
       <c r="R49" s="17"/>
       <c r="S49" s="17"/>
       <c r="T49" s="17"/>
@@ -15647,9 +15612,7 @@
       <c r="N50" s="10"/>
       <c r="O50" s="11"/>
       <c r="P50" s="16"/>
-      <c r="Q50" s="17" t="s">
-        <v>78</v>
-      </c>
+      <c r="Q50" s="17"/>
       <c r="R50" s="17"/>
       <c r="S50" s="17"/>
       <c r="T50" s="17"/>
@@ -15893,63 +15856,67 @@
       <c r="IX50" s="1"/>
     </row>
     <row r="51" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="T51" s="17"/>
-      <c r="U51" s="17"/>
-      <c r="V51" s="17"/>
-      <c r="W51" s="17"/>
-      <c r="X51" s="17"/>
-      <c r="Y51" s="17"/>
-      <c r="Z51" s="17"/>
-      <c r="AA51" s="17"/>
-      <c r="AB51" s="17"/>
-      <c r="AC51" s="17"/>
-      <c r="AD51" s="17"/>
-      <c r="AE51" s="17"/>
-      <c r="AF51" s="17"/>
-      <c r="AG51" s="17"/>
-      <c r="AH51" s="17"/>
-      <c r="AI51" s="17"/>
-      <c r="AJ51" s="17"/>
-      <c r="AK51" s="17"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51" s="17"/>
-      <c r="AN51" s="17"/>
-      <c r="AO51" s="17"/>
-      <c r="AP51" s="17"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17"/>
-      <c r="AS51" s="18"/>
-      <c r="AT51" s="8"/>
-      <c r="AU51" s="10"/>
-      <c r="AV51" s="9"/>
-      <c r="AW51" s="10"/>
-      <c r="AX51" s="10"/>
-      <c r="AY51" s="10"/>
-      <c r="AZ51" s="10"/>
-      <c r="BA51" s="10"/>
-      <c r="BB51" s="10"/>
-      <c r="BC51" s="10"/>
-      <c r="BD51" s="10"/>
-      <c r="BE51" s="10"/>
-      <c r="BF51" s="10"/>
-      <c r="BG51" s="10"/>
-      <c r="BH51" s="10"/>
-      <c r="BI51" s="11"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="25"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="26"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="27"/>
+      <c r="R51" s="27"/>
+      <c r="S51" s="27"/>
+      <c r="T51" s="27"/>
+      <c r="U51" s="27"/>
+      <c r="V51" s="27"/>
+      <c r="W51" s="27"/>
+      <c r="X51" s="27"/>
+      <c r="Y51" s="27"/>
+      <c r="Z51" s="27"/>
+      <c r="AA51" s="27"/>
+      <c r="AB51" s="27"/>
+      <c r="AC51" s="27"/>
+      <c r="AD51" s="27"/>
+      <c r="AE51" s="27"/>
+      <c r="AF51" s="27"/>
+      <c r="AG51" s="27"/>
+      <c r="AH51" s="27"/>
+      <c r="AI51" s="27"/>
+      <c r="AJ51" s="27"/>
+      <c r="AK51" s="27"/>
+      <c r="AL51" s="27"/>
+      <c r="AM51" s="27"/>
+      <c r="AN51" s="27"/>
+      <c r="AO51" s="27"/>
+      <c r="AP51" s="27"/>
+      <c r="AQ51" s="27"/>
+      <c r="AR51" s="27"/>
+      <c r="AS51" s="28"/>
+      <c r="AT51" s="24"/>
+      <c r="AU51" s="25"/>
+      <c r="AV51" s="31"/>
+      <c r="AW51" s="25"/>
+      <c r="AX51" s="25"/>
+      <c r="AY51" s="25"/>
+      <c r="AZ51" s="25"/>
+      <c r="BA51" s="25"/>
+      <c r="BB51" s="25"/>
+      <c r="BC51" s="25"/>
+      <c r="BD51" s="25"/>
+      <c r="BE51" s="25"/>
+      <c r="BF51" s="25"/>
+      <c r="BG51" s="25"/>
+      <c r="BH51" s="25"/>
+      <c r="BI51" s="26"/>
       <c r="BJ51" s="1"/>
       <c r="BK51" s="1"/>
       <c r="BL51" s="1"/>
@@ -16149,61 +16116,67 @@
       <c r="IX51" s="1"/>
     </row>
     <row r="52" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-      <c r="V52" s="17"/>
-      <c r="W52" s="17"/>
-      <c r="X52" s="17"/>
-      <c r="Y52" s="17"/>
-      <c r="Z52" s="17"/>
-      <c r="AA52" s="17"/>
-      <c r="AB52" s="17"/>
-      <c r="AC52" s="17"/>
-      <c r="AD52" s="17"/>
-      <c r="AE52" s="17"/>
-      <c r="AF52" s="17"/>
-      <c r="AG52" s="17"/>
-      <c r="AH52" s="17"/>
-      <c r="AI52" s="17"/>
-      <c r="AJ52" s="17"/>
-      <c r="AK52" s="17"/>
-      <c r="AL52" s="17"/>
-      <c r="AM52" s="17"/>
-      <c r="AN52" s="17"/>
-      <c r="AO52" s="17"/>
-      <c r="AP52" s="17"/>
-      <c r="AQ52" s="17"/>
-      <c r="AR52" s="17"/>
-      <c r="AS52" s="18"/>
-      <c r="AT52" s="8"/>
-      <c r="AU52" s="10"/>
-      <c r="AV52" s="9"/>
-      <c r="AW52" s="10"/>
-      <c r="AX52" s="10"/>
-      <c r="AY52" s="10"/>
-      <c r="AZ52" s="10"/>
-      <c r="BA52" s="10"/>
-      <c r="BB52" s="10"/>
-      <c r="BC52" s="10"/>
-      <c r="BD52" s="10"/>
-      <c r="BE52" s="10"/>
-      <c r="BF52" s="10"/>
-      <c r="BG52" s="10"/>
-      <c r="BH52" s="10"/>
-      <c r="BI52" s="11"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="13"/>
+      <c r="U52" s="13"/>
+      <c r="V52" s="13"/>
+      <c r="W52" s="13"/>
+      <c r="X52" s="13"/>
+      <c r="Y52" s="13"/>
+      <c r="Z52" s="13"/>
+      <c r="AA52" s="13"/>
+      <c r="AB52" s="13"/>
+      <c r="AC52" s="13"/>
+      <c r="AD52" s="13"/>
+      <c r="AE52" s="13"/>
+      <c r="AF52" s="13"/>
+      <c r="AG52" s="13"/>
+      <c r="AH52" s="13"/>
+      <c r="AI52" s="13"/>
+      <c r="AJ52" s="13"/>
+      <c r="AK52" s="13"/>
+      <c r="AL52" s="13"/>
+      <c r="AM52" s="13"/>
+      <c r="AN52" s="13"/>
+      <c r="AO52" s="13"/>
+      <c r="AP52" s="13"/>
+      <c r="AQ52" s="13"/>
+      <c r="AR52" s="13"/>
+      <c r="AS52" s="13"/>
+      <c r="AT52" s="13"/>
+      <c r="AU52" s="13"/>
+      <c r="AV52" s="13"/>
+      <c r="AW52" s="13"/>
+      <c r="AX52" s="13"/>
+      <c r="AY52" s="13"/>
+      <c r="AZ52" s="13"/>
+      <c r="BA52" s="13"/>
+      <c r="BB52" s="13"/>
+      <c r="BC52" s="13"/>
+      <c r="BD52" s="13"/>
+      <c r="BE52" s="13"/>
+      <c r="BF52" s="13"/>
+      <c r="BG52" s="13"/>
+      <c r="BH52" s="13"/>
+      <c r="BI52" s="13"/>
       <c r="BJ52" s="1"/>
       <c r="BK52" s="1"/>
       <c r="BL52" s="1"/>
@@ -16402,528 +16375,30 @@
       <c r="IW52" s="1"/>
       <c r="IX52" s="1"/>
     </row>
-    <row r="53" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="24"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="25"/>
-      <c r="J53" s="25"/>
-      <c r="K53" s="25"/>
-      <c r="L53" s="25"/>
-      <c r="M53" s="25"/>
-      <c r="N53" s="25"/>
-      <c r="O53" s="26"/>
-      <c r="P53" s="30"/>
-      <c r="Q53" s="27"/>
-      <c r="R53" s="27"/>
-      <c r="S53" s="27"/>
-      <c r="T53" s="27"/>
-      <c r="U53" s="27"/>
-      <c r="V53" s="27"/>
-      <c r="W53" s="27"/>
-      <c r="X53" s="27"/>
-      <c r="Y53" s="27"/>
-      <c r="Z53" s="27"/>
-      <c r="AA53" s="27"/>
-      <c r="AB53" s="27"/>
-      <c r="AC53" s="27"/>
-      <c r="AD53" s="27"/>
-      <c r="AE53" s="27"/>
-      <c r="AF53" s="27"/>
-      <c r="AG53" s="27"/>
-      <c r="AH53" s="27"/>
-      <c r="AI53" s="27"/>
-      <c r="AJ53" s="27"/>
-      <c r="AK53" s="27"/>
-      <c r="AL53" s="27"/>
-      <c r="AM53" s="27"/>
-      <c r="AN53" s="27"/>
-      <c r="AO53" s="27"/>
-      <c r="AP53" s="27"/>
-      <c r="AQ53" s="27"/>
-      <c r="AR53" s="27"/>
-      <c r="AS53" s="28"/>
-      <c r="AT53" s="24"/>
-      <c r="AU53" s="25"/>
-      <c r="AV53" s="31"/>
-      <c r="AW53" s="25"/>
-      <c r="AX53" s="25"/>
-      <c r="AY53" s="25"/>
-      <c r="AZ53" s="25"/>
-      <c r="BA53" s="25"/>
-      <c r="BB53" s="25"/>
-      <c r="BC53" s="25"/>
-      <c r="BD53" s="25"/>
-      <c r="BE53" s="25"/>
-      <c r="BF53" s="25"/>
-      <c r="BG53" s="25"/>
-      <c r="BH53" s="25"/>
-      <c r="BI53" s="26"/>
-      <c r="BJ53" s="1"/>
-      <c r="BK53" s="1"/>
-      <c r="BL53" s="1"/>
-      <c r="BM53" s="1"/>
-      <c r="BN53" s="1"/>
-      <c r="BO53" s="1"/>
-      <c r="BP53" s="1"/>
-      <c r="BQ53" s="1"/>
-      <c r="BR53" s="1"/>
-      <c r="BS53" s="1"/>
-      <c r="BT53" s="1"/>
-      <c r="BU53" s="1"/>
-      <c r="BV53" s="1"/>
-      <c r="BW53" s="1"/>
-      <c r="BX53" s="1"/>
-      <c r="BY53" s="1"/>
-      <c r="BZ53" s="1"/>
-      <c r="CA53" s="1"/>
-      <c r="CB53" s="1"/>
-      <c r="CC53" s="1"/>
-      <c r="CD53" s="1"/>
-      <c r="CE53" s="1"/>
-      <c r="CF53" s="1"/>
-      <c r="CG53" s="1"/>
-      <c r="CH53" s="1"/>
-      <c r="CI53" s="1"/>
-      <c r="CJ53" s="1"/>
-      <c r="CK53" s="1"/>
-      <c r="CL53" s="1"/>
-      <c r="CM53" s="1"/>
-      <c r="CN53" s="1"/>
-      <c r="CO53" s="1"/>
-      <c r="CP53" s="1"/>
-      <c r="CQ53" s="1"/>
-      <c r="CR53" s="1"/>
-      <c r="CS53" s="1"/>
-      <c r="CT53" s="1"/>
-      <c r="CU53" s="1"/>
-      <c r="CV53" s="1"/>
-      <c r="CW53" s="1"/>
-      <c r="CX53" s="1"/>
-      <c r="CY53" s="1"/>
-      <c r="CZ53" s="1"/>
-      <c r="DA53" s="1"/>
-      <c r="DB53" s="1"/>
-      <c r="DC53" s="1"/>
-      <c r="DD53" s="1"/>
-      <c r="DE53" s="1"/>
-      <c r="DF53" s="1"/>
-      <c r="DG53" s="1"/>
-      <c r="DH53" s="1"/>
-      <c r="DI53" s="1"/>
-      <c r="DJ53" s="1"/>
-      <c r="DK53" s="1"/>
-      <c r="DL53" s="1"/>
-      <c r="DM53" s="1"/>
-      <c r="DN53" s="1"/>
-      <c r="DO53" s="1"/>
-      <c r="DP53" s="1"/>
-      <c r="DQ53" s="1"/>
-      <c r="DR53" s="1"/>
-      <c r="DS53" s="1"/>
-      <c r="DT53" s="1"/>
-      <c r="DU53" s="1"/>
-      <c r="DV53" s="1"/>
-      <c r="DW53" s="1"/>
-      <c r="DX53" s="1"/>
-      <c r="DY53" s="1"/>
-      <c r="DZ53" s="1"/>
-      <c r="EA53" s="1"/>
-      <c r="EB53" s="1"/>
-      <c r="EC53" s="1"/>
-      <c r="ED53" s="1"/>
-      <c r="EE53" s="1"/>
-      <c r="EF53" s="1"/>
-      <c r="EG53" s="1"/>
-      <c r="EH53" s="1"/>
-      <c r="EI53" s="1"/>
-      <c r="EJ53" s="1"/>
-      <c r="EK53" s="1"/>
-      <c r="EL53" s="1"/>
-      <c r="EM53" s="1"/>
-      <c r="EN53" s="1"/>
-      <c r="EO53" s="1"/>
-      <c r="EP53" s="1"/>
-      <c r="EQ53" s="1"/>
-      <c r="ER53" s="1"/>
-      <c r="ES53" s="1"/>
-      <c r="ET53" s="1"/>
-      <c r="EU53" s="1"/>
-      <c r="EV53" s="1"/>
-      <c r="EW53" s="1"/>
-      <c r="EX53" s="1"/>
-      <c r="EY53" s="1"/>
-      <c r="EZ53" s="1"/>
-      <c r="FA53" s="1"/>
-      <c r="FB53" s="1"/>
-      <c r="FC53" s="1"/>
-      <c r="FD53" s="1"/>
-      <c r="FE53" s="1"/>
-      <c r="FF53" s="1"/>
-      <c r="FG53" s="1"/>
-      <c r="FH53" s="1"/>
-      <c r="FI53" s="1"/>
-      <c r="FJ53" s="1"/>
-      <c r="FK53" s="1"/>
-      <c r="FL53" s="1"/>
-      <c r="FM53" s="1"/>
-      <c r="FN53" s="1"/>
-      <c r="FO53" s="1"/>
-      <c r="FP53" s="1"/>
-      <c r="FQ53" s="1"/>
-      <c r="FR53" s="1"/>
-      <c r="FS53" s="1"/>
-      <c r="FT53" s="1"/>
-      <c r="FU53" s="1"/>
-      <c r="FV53" s="1"/>
-      <c r="FW53" s="1"/>
-      <c r="FX53" s="1"/>
-      <c r="FY53" s="1"/>
-      <c r="FZ53" s="1"/>
-      <c r="GA53" s="1"/>
-      <c r="GB53" s="1"/>
-      <c r="GC53" s="1"/>
-      <c r="GD53" s="1"/>
-      <c r="GE53" s="1"/>
-      <c r="GF53" s="1"/>
-      <c r="GG53" s="1"/>
-      <c r="GH53" s="1"/>
-      <c r="GI53" s="1"/>
-      <c r="GJ53" s="1"/>
-      <c r="GK53" s="1"/>
-      <c r="GL53" s="1"/>
-      <c r="GM53" s="1"/>
-      <c r="GN53" s="1"/>
-      <c r="GO53" s="1"/>
-      <c r="GP53" s="1"/>
-      <c r="GQ53" s="1"/>
-      <c r="GR53" s="1"/>
-      <c r="GS53" s="1"/>
-      <c r="GT53" s="1"/>
-      <c r="GU53" s="1"/>
-      <c r="GV53" s="1"/>
-      <c r="GW53" s="1"/>
-      <c r="GX53" s="1"/>
-      <c r="GY53" s="1"/>
-      <c r="GZ53" s="1"/>
-      <c r="HA53" s="1"/>
-      <c r="HB53" s="1"/>
-      <c r="HC53" s="1"/>
-      <c r="HD53" s="1"/>
-      <c r="HE53" s="1"/>
-      <c r="HF53" s="1"/>
-      <c r="HG53" s="1"/>
-      <c r="HH53" s="1"/>
-      <c r="HI53" s="1"/>
-      <c r="HJ53" s="1"/>
-      <c r="HK53" s="1"/>
-      <c r="HL53" s="1"/>
-      <c r="HM53" s="1"/>
-      <c r="HN53" s="1"/>
-      <c r="HO53" s="1"/>
-      <c r="HP53" s="1"/>
-      <c r="HQ53" s="1"/>
-      <c r="HR53" s="1"/>
-      <c r="HS53" s="1"/>
-      <c r="HT53" s="1"/>
-      <c r="HU53" s="1"/>
-      <c r="HV53" s="1"/>
-      <c r="HW53" s="1"/>
-      <c r="HX53" s="1"/>
-      <c r="HY53" s="1"/>
-      <c r="HZ53" s="1"/>
-      <c r="IA53" s="1"/>
-      <c r="IB53" s="1"/>
-      <c r="IC53" s="1"/>
-      <c r="ID53" s="1"/>
-      <c r="IE53" s="1"/>
-      <c r="IF53" s="1"/>
-      <c r="IG53" s="1"/>
-      <c r="IH53" s="1"/>
-      <c r="II53" s="1"/>
-      <c r="IJ53" s="1"/>
-      <c r="IK53" s="1"/>
-      <c r="IL53" s="1"/>
-      <c r="IM53" s="1"/>
-      <c r="IN53" s="1"/>
-      <c r="IO53" s="1"/>
-      <c r="IP53" s="1"/>
-      <c r="IQ53" s="1"/>
-      <c r="IR53" s="1"/>
-      <c r="IS53" s="1"/>
-      <c r="IT53" s="1"/>
-      <c r="IU53" s="1"/>
-      <c r="IV53" s="1"/>
-      <c r="IW53" s="1"/>
-      <c r="IX53" s="1"/>
-    </row>
-    <row r="54" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
-      <c r="L54" s="13"/>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="13"/>
-      <c r="Q54" s="13"/>
-      <c r="R54" s="13"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="13"/>
-      <c r="U54" s="13"/>
-      <c r="V54" s="13"/>
-      <c r="W54" s="13"/>
-      <c r="X54" s="13"/>
-      <c r="Y54" s="13"/>
-      <c r="Z54" s="13"/>
-      <c r="AA54" s="13"/>
-      <c r="AB54" s="13"/>
-      <c r="AC54" s="13"/>
-      <c r="AD54" s="13"/>
-      <c r="AE54" s="13"/>
-      <c r="AF54" s="13"/>
-      <c r="AG54" s="13"/>
-      <c r="AH54" s="13"/>
-      <c r="AI54" s="13"/>
-      <c r="AJ54" s="13"/>
-      <c r="AK54" s="13"/>
-      <c r="AL54" s="13"/>
-      <c r="AM54" s="13"/>
-      <c r="AN54" s="13"/>
-      <c r="AO54" s="13"/>
-      <c r="AP54" s="13"/>
-      <c r="AQ54" s="13"/>
-      <c r="AR54" s="13"/>
-      <c r="AS54" s="13"/>
-      <c r="AT54" s="13"/>
-      <c r="AU54" s="13"/>
-      <c r="AV54" s="13"/>
-      <c r="AW54" s="13"/>
-      <c r="AX54" s="13"/>
-      <c r="AY54" s="13"/>
-      <c r="AZ54" s="13"/>
-      <c r="BA54" s="13"/>
-      <c r="BB54" s="13"/>
-      <c r="BC54" s="13"/>
-      <c r="BD54" s="13"/>
-      <c r="BE54" s="13"/>
-      <c r="BF54" s="13"/>
-      <c r="BG54" s="13"/>
-      <c r="BH54" s="13"/>
-      <c r="BI54" s="13"/>
-      <c r="BJ54" s="1"/>
-      <c r="BK54" s="1"/>
-      <c r="BL54" s="1"/>
-      <c r="BM54" s="1"/>
-      <c r="BN54" s="1"/>
-      <c r="BO54" s="1"/>
-      <c r="BP54" s="1"/>
-      <c r="BQ54" s="1"/>
-      <c r="BR54" s="1"/>
-      <c r="BS54" s="1"/>
-      <c r="BT54" s="1"/>
-      <c r="BU54" s="1"/>
-      <c r="BV54" s="1"/>
-      <c r="BW54" s="1"/>
-      <c r="BX54" s="1"/>
-      <c r="BY54" s="1"/>
-      <c r="BZ54" s="1"/>
-      <c r="CA54" s="1"/>
-      <c r="CB54" s="1"/>
-      <c r="CC54" s="1"/>
-      <c r="CD54" s="1"/>
-      <c r="CE54" s="1"/>
-      <c r="CF54" s="1"/>
-      <c r="CG54" s="1"/>
-      <c r="CH54" s="1"/>
-      <c r="CI54" s="1"/>
-      <c r="CJ54" s="1"/>
-      <c r="CK54" s="1"/>
-      <c r="CL54" s="1"/>
-      <c r="CM54" s="1"/>
-      <c r="CN54" s="1"/>
-      <c r="CO54" s="1"/>
-      <c r="CP54" s="1"/>
-      <c r="CQ54" s="1"/>
-      <c r="CR54" s="1"/>
-      <c r="CS54" s="1"/>
-      <c r="CT54" s="1"/>
-      <c r="CU54" s="1"/>
-      <c r="CV54" s="1"/>
-      <c r="CW54" s="1"/>
-      <c r="CX54" s="1"/>
-      <c r="CY54" s="1"/>
-      <c r="CZ54" s="1"/>
-      <c r="DA54" s="1"/>
-      <c r="DB54" s="1"/>
-      <c r="DC54" s="1"/>
-      <c r="DD54" s="1"/>
-      <c r="DE54" s="1"/>
-      <c r="DF54" s="1"/>
-      <c r="DG54" s="1"/>
-      <c r="DH54" s="1"/>
-      <c r="DI54" s="1"/>
-      <c r="DJ54" s="1"/>
-      <c r="DK54" s="1"/>
-      <c r="DL54" s="1"/>
-      <c r="DM54" s="1"/>
-      <c r="DN54" s="1"/>
-      <c r="DO54" s="1"/>
-      <c r="DP54" s="1"/>
-      <c r="DQ54" s="1"/>
-      <c r="DR54" s="1"/>
-      <c r="DS54" s="1"/>
-      <c r="DT54" s="1"/>
-      <c r="DU54" s="1"/>
-      <c r="DV54" s="1"/>
-      <c r="DW54" s="1"/>
-      <c r="DX54" s="1"/>
-      <c r="DY54" s="1"/>
-      <c r="DZ54" s="1"/>
-      <c r="EA54" s="1"/>
-      <c r="EB54" s="1"/>
-      <c r="EC54" s="1"/>
-      <c r="ED54" s="1"/>
-      <c r="EE54" s="1"/>
-      <c r="EF54" s="1"/>
-      <c r="EG54" s="1"/>
-      <c r="EH54" s="1"/>
-      <c r="EI54" s="1"/>
-      <c r="EJ54" s="1"/>
-      <c r="EK54" s="1"/>
-      <c r="EL54" s="1"/>
-      <c r="EM54" s="1"/>
-      <c r="EN54" s="1"/>
-      <c r="EO54" s="1"/>
-      <c r="EP54" s="1"/>
-      <c r="EQ54" s="1"/>
-      <c r="ER54" s="1"/>
-      <c r="ES54" s="1"/>
-      <c r="ET54" s="1"/>
-      <c r="EU54" s="1"/>
-      <c r="EV54" s="1"/>
-      <c r="EW54" s="1"/>
-      <c r="EX54" s="1"/>
-      <c r="EY54" s="1"/>
-      <c r="EZ54" s="1"/>
-      <c r="FA54" s="1"/>
-      <c r="FB54" s="1"/>
-      <c r="FC54" s="1"/>
-      <c r="FD54" s="1"/>
-      <c r="FE54" s="1"/>
-      <c r="FF54" s="1"/>
-      <c r="FG54" s="1"/>
-      <c r="FH54" s="1"/>
-      <c r="FI54" s="1"/>
-      <c r="FJ54" s="1"/>
-      <c r="FK54" s="1"/>
-      <c r="FL54" s="1"/>
-      <c r="FM54" s="1"/>
-      <c r="FN54" s="1"/>
-      <c r="FO54" s="1"/>
-      <c r="FP54" s="1"/>
-      <c r="FQ54" s="1"/>
-      <c r="FR54" s="1"/>
-      <c r="FS54" s="1"/>
-      <c r="FT54" s="1"/>
-      <c r="FU54" s="1"/>
-      <c r="FV54" s="1"/>
-      <c r="FW54" s="1"/>
-      <c r="FX54" s="1"/>
-      <c r="FY54" s="1"/>
-      <c r="FZ54" s="1"/>
-      <c r="GA54" s="1"/>
-      <c r="GB54" s="1"/>
-      <c r="GC54" s="1"/>
-      <c r="GD54" s="1"/>
-      <c r="GE54" s="1"/>
-      <c r="GF54" s="1"/>
-      <c r="GG54" s="1"/>
-      <c r="GH54" s="1"/>
-      <c r="GI54" s="1"/>
-      <c r="GJ54" s="1"/>
-      <c r="GK54" s="1"/>
-      <c r="GL54" s="1"/>
-      <c r="GM54" s="1"/>
-      <c r="GN54" s="1"/>
-      <c r="GO54" s="1"/>
-      <c r="GP54" s="1"/>
-      <c r="GQ54" s="1"/>
-      <c r="GR54" s="1"/>
-      <c r="GS54" s="1"/>
-      <c r="GT54" s="1"/>
-      <c r="GU54" s="1"/>
-      <c r="GV54" s="1"/>
-      <c r="GW54" s="1"/>
-      <c r="GX54" s="1"/>
-      <c r="GY54" s="1"/>
-      <c r="GZ54" s="1"/>
-      <c r="HA54" s="1"/>
-      <c r="HB54" s="1"/>
-      <c r="HC54" s="1"/>
-      <c r="HD54" s="1"/>
-      <c r="HE54" s="1"/>
-      <c r="HF54" s="1"/>
-      <c r="HG54" s="1"/>
-      <c r="HH54" s="1"/>
-      <c r="HI54" s="1"/>
-      <c r="HJ54" s="1"/>
-      <c r="HK54" s="1"/>
-      <c r="HL54" s="1"/>
-      <c r="HM54" s="1"/>
-      <c r="HN54" s="1"/>
-      <c r="HO54" s="1"/>
-      <c r="HP54" s="1"/>
-      <c r="HQ54" s="1"/>
-      <c r="HR54" s="1"/>
-      <c r="HS54" s="1"/>
-      <c r="HT54" s="1"/>
-      <c r="HU54" s="1"/>
-      <c r="HV54" s="1"/>
-      <c r="HW54" s="1"/>
-      <c r="HX54" s="1"/>
-      <c r="HY54" s="1"/>
-      <c r="HZ54" s="1"/>
-      <c r="IA54" s="1"/>
-      <c r="IB54" s="1"/>
-      <c r="IC54" s="1"/>
-      <c r="ID54" s="1"/>
-      <c r="IE54" s="1"/>
-      <c r="IF54" s="1"/>
-      <c r="IG54" s="1"/>
-      <c r="IH54" s="1"/>
-      <c r="II54" s="1"/>
-      <c r="IJ54" s="1"/>
-      <c r="IK54" s="1"/>
-      <c r="IL54" s="1"/>
-      <c r="IM54" s="1"/>
-      <c r="IN54" s="1"/>
-      <c r="IO54" s="1"/>
-      <c r="IP54" s="1"/>
-      <c r="IQ54" s="1"/>
-      <c r="IR54" s="1"/>
-      <c r="IS54" s="1"/>
-      <c r="IT54" s="1"/>
-      <c r="IU54" s="1"/>
-      <c r="IV54" s="1"/>
-      <c r="IW54" s="1"/>
-      <c r="IX54" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="P12:AS12"/>
+    <mergeCell ref="AT12:BI12"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:BI10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
     <mergeCell ref="A5:F5"/>
@@ -16940,28 +16415,6 @@
     <mergeCell ref="BA1:BC1"/>
     <mergeCell ref="BD1:BI1"/>
     <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="P12:AS12"/>
-    <mergeCell ref="AT12:BI12"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:BI10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
@@ -16986,12 +16439,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -17123,6 +16570,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
   <ds:schemaRefs>
@@ -17132,15 +16585,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7560E91F-1ABF-4BEF-A078-A8FA5AD9AA18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17156,4 +16600,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>